--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0CF0224-07FA-43FC-802E-19158D8B1734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6D0932-4E75-4675-815F-E2F4517AC66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -1582,15 +1582,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.3046875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1601,7 +1601,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1680,7 +1680,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1691,7 +1691,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -1713,7 +1713,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1735,7 +1735,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1779,19 +1779,19 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46248.30673773148</v>
+        <v>46249.373742592594</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1813,7 +1813,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>95</v>
       </c>
@@ -1868,34 +1868,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA14"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="55.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="55" style="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="49.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="31"/>
+    <col min="1" max="1" width="1.921875" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.921875" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="40.07421875" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.4609375" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.07421875" style="31" customWidth="1"/>
+    <col min="21" max="21" width="5.69140625" style="31" customWidth="1"/>
+    <col min="22" max="22" width="8.765625" style="31" customWidth="1"/>
+    <col min="23" max="23" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.61328125" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.07421875" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="36" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -1978,7 +1979,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="35">
         <v>2</v>
       </c>
@@ -2070,7 +2071,7 @@
         <v>A calendar date for an event that happened or will happen.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="35">
         <v>3</v>
       </c>
@@ -2163,7 +2164,7 @@
         <v>It is a standard drone-type aircraft or UAS.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="35">
         <v>4</v>
       </c>
@@ -2256,7 +2257,7 @@
         <v>It is a drone-type aircraft or UAS with a built-in LIDAR (Light Detection and Ranging) device.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="35">
         <v>5</v>
       </c>
@@ -2349,7 +2350,7 @@
         <v>Autonomous flight plan.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="35">
         <v>6</v>
       </c>
@@ -2442,7 +2443,7 @@
         <v>Autonomous flight carried out with a drone.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="35">
         <v>7</v>
       </c>
@@ -2535,7 +2536,7 @@
         <v>Manual flight carried out with drone.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="35">
         <v>8</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>Inspection carried out in the field.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="35">
         <v>9</v>
       </c>
@@ -2721,7 +2722,7 @@
         <v>Photographic Image Bank corresponding to a Maintenance Flight performed.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="35">
         <v>10</v>
       </c>
@@ -2814,7 +2815,7 @@
         <v>Photographic image corresponding to a WayPoint.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="35">
         <v>11</v>
       </c>
@@ -2907,7 +2908,7 @@
         <v>Video recorded during a flight.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="35">
         <v>12</v>
       </c>
@@ -3000,7 +3001,7 @@
         <v>Drone flight planned to take conservation actions of building systems.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="35">
         <v>13</v>
       </c>
@@ -3093,7 +3094,7 @@
         <v>Drone flight planned to take corrective actions for pathologies.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="35">
         <v>14</v>
       </c>
@@ -3229,14 +3230,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.7109375" style="12"/>
-    <col min="11" max="16384" width="5.7109375" style="16"/>
+    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.69140625" style="12"/>
+    <col min="11" max="16384" width="5.69140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3301,7 +3302,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -3375,16 +3376,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="2" max="2" width="7.84375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.69140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.3828125" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -3398,7 +3399,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3420,38 +3421,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72143BD-9EBA-4CBF-96E5-A46CFFC881A3}">
   <dimension ref="A1:AA29"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.53515625" customWidth="1"/>
+    <col min="3" max="3" width="8.69140625" customWidth="1"/>
+    <col min="4" max="4" width="7.15234375" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="7" width="4.85546875" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" customWidth="1"/>
-    <col min="10" max="10" width="3.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.84375" customWidth="1"/>
+    <col min="7" max="7" width="4.84375" customWidth="1"/>
+    <col min="8" max="8" width="7.15234375" customWidth="1"/>
+    <col min="9" max="9" width="7.3046875" customWidth="1"/>
+    <col min="10" max="10" width="3.69140625" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="3.140625" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="4.5703125" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" customWidth="1"/>
-    <col min="16" max="16" width="5.42578125" customWidth="1"/>
-    <col min="17" max="17" width="28.85546875" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" customWidth="1"/>
-    <col min="19" max="19" width="31.85546875" customWidth="1"/>
-    <col min="20" max="20" width="2.85546875" customWidth="1"/>
-    <col min="21" max="21" width="7.28515625" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" customWidth="1"/>
-    <col min="26" max="26" width="6.28515625" customWidth="1"/>
-    <col min="27" max="27" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="3.15234375" customWidth="1"/>
+    <col min="13" max="13" width="14.53515625" customWidth="1"/>
+    <col min="14" max="14" width="4.53515625" customWidth="1"/>
+    <col min="15" max="15" width="7.15234375" customWidth="1"/>
+    <col min="16" max="16" width="5.3828125" customWidth="1"/>
+    <col min="17" max="17" width="28.84375" customWidth="1"/>
+    <col min="18" max="18" width="6.3828125" customWidth="1"/>
+    <col min="19" max="19" width="31.84375" customWidth="1"/>
+    <col min="20" max="20" width="2.84375" customWidth="1"/>
+    <col min="21" max="21" width="7.3046875" customWidth="1"/>
+    <col min="22" max="22" width="6.69140625" customWidth="1"/>
+    <col min="23" max="23" width="9.53515625" customWidth="1"/>
+    <col min="24" max="24" width="4.84375" customWidth="1"/>
+    <col min="25" max="25" width="7.3828125" customWidth="1"/>
+    <col min="26" max="26" width="6.3046875" customWidth="1"/>
+    <col min="27" max="27" width="10.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="36" t="s">
         <v>108</v>
       </c>
@@ -3534,7 +3535,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -3617,7 +3618,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -3700,7 +3701,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -3783,7 +3784,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -3866,7 +3867,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -3949,7 +3950,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -4032,7 +4033,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -4115,7 +4116,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -4281,7 +4282,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -4364,7 +4365,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -4447,7 +4448,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -4530,7 +4531,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -4613,7 +4614,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -4696,7 +4697,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -4779,7 +4780,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -4862,7 +4863,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -4945,7 +4946,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -5028,7 +5029,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -5111,7 +5112,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -5194,7 +5195,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -5277,7 +5278,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -5360,7 +5361,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -5443,7 +5444,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -5526,7 +5527,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -5609,7 +5610,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -5692,7 +5693,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -5775,7 +5776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="43">
         <v>29</v>
       </c>

--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6D0932-4E75-4675-815F-E2F4517AC66B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F48C74-B462-4BCF-87F3-CB6CD902F029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="231">
   <si>
     <t>Edição</t>
   </si>
@@ -349,9 +349,6 @@
     <t>ClasseIfc</t>
   </si>
   <si>
-    <t>ABNT</t>
-  </si>
-  <si>
     <t>000 Translate Classe 5</t>
   </si>
   <si>
@@ -680,6 +677,93 @@
   </si>
   <si>
     <t>Diagnósticas</t>
+  </si>
+  <si>
+    <t>A calendar date for an event that happened or will happen.</t>
+  </si>
+  <si>
+    <t>It is a standard drone-type aircraft or UAS.</t>
+  </si>
+  <si>
+    <t>It is a drone-type aircraft or UAS with a built-in LIDAR (Light Detection and Ranging) device.</t>
+  </si>
+  <si>
+    <t>Autonomous flight plan.</t>
+  </si>
+  <si>
+    <t>Autonomous flight carried out with a drone.</t>
+  </si>
+  <si>
+    <t>Manual flight carried out with drone.</t>
+  </si>
+  <si>
+    <t>Inspection carried out in the field.</t>
+  </si>
+  <si>
+    <t>Photographic Image Bank corresponding to a Maintenance Flight performed.</t>
+  </si>
+  <si>
+    <t>Photographic image corresponding to a WayPoint.</t>
+  </si>
+  <si>
+    <t>Video recorded during a flight.</t>
+  </si>
+  <si>
+    <t>Drone flight planned to take conservation actions of building systems.</t>
+  </si>
+  <si>
+    <t>Drone flight planned to take corrective actions for pathologies.</t>
+  </si>
+  <si>
+    <t>Planned drone flight to predict future maintenance or pathologies.</t>
+  </si>
+  <si>
+    <t>Es una aeronave estándar de tipo dron o UAS.</t>
+  </si>
+  <si>
+    <t>Es una aeronave tipo dron o UAS con un dispositivo LIDAR (Detección y Alcance de Luz) incorporado.</t>
+  </si>
+  <si>
+    <t>Plan de vuelo autónomo.</t>
+  </si>
+  <si>
+    <t>Vuelo autónomo realizado con un dron.</t>
+  </si>
+  <si>
+    <t>El vuelo manual se realiza con dron.</t>
+  </si>
+  <si>
+    <t>Inspección realizada en el terreno.</t>
+  </si>
+  <si>
+    <t>Banco de Imágenes Fotográficas correspondiente a un vuelo de mantenimiento realizado.</t>
+  </si>
+  <si>
+    <t>Imagen fotográfica correspondiente a un WayPoint.</t>
+  </si>
+  <si>
+    <t>Vídeo grabado durante un vuelo.</t>
+  </si>
+  <si>
+    <t>El vuelo con drones planeó realizar acciones de conservación de los sistemas del edificio.</t>
+  </si>
+  <si>
+    <t>El vuelo de drones planeó tomar medidas correctivas para patologías.</t>
+  </si>
+  <si>
+    <t>Vuelo planificado con dron para predecir el mantenimiento futuro o patologías.</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Código ABNT</t>
+  </si>
+  <si>
+    <t>Atributo Ifc</t>
   </si>
 </sst>
 </file>
@@ -1137,7 +1221,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="14">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1147,6 +1231,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1582,15 +1674,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.3046875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="13"/>
+    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1598,10 +1690,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1609,10 +1701,10 @@
         <v>74</v>
       </c>
       <c r="C2" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1620,10 +1712,10 @@
         <v>86</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1631,10 +1723,10 @@
         <v>16</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1643,10 +1735,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1655,10 +1747,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1666,21 +1758,21 @@
         <v>27</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1688,10 +1780,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1699,10 +1791,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -1710,10 +1802,10 @@
         <v>12</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1721,10 +1813,10 @@
         <v>12</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1732,10 +1824,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1743,10 +1835,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1754,10 +1846,10 @@
         <v>12</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -1765,10 +1857,10 @@
         <v>12</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1776,22 +1868,22 @@
         <v>87</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46249.373742592594</v>
+        <v>46253.628990972225</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1799,10 +1891,10 @@
         <v>12</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1810,10 +1902,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -1821,10 +1913,10 @@
         <v>12</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -1832,10 +1924,10 @@
         <v>88</v>
       </c>
       <c r="C22" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -1844,19 +1936,19 @@
         <v>Formalizar los datos de los vuelos de drones.</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize data for drone flights.</v>
       </c>
       <c r="C24" s="27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1867,36 +1959,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA14"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC14"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.921875" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.3828125" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.921875" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="31" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.3828125" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="40.07421875" style="31" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="40" style="31" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.4609375" style="31" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.07421875" style="31" customWidth="1"/>
-    <col min="21" max="21" width="5.69140625" style="31" customWidth="1"/>
-    <col min="22" max="22" width="8.765625" style="31" customWidth="1"/>
-    <col min="23" max="23" width="5.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.61328125" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.3828125" style="31" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.07421875" style="31" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="36" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="31"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="55.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="46" style="31" customWidth="1"/>
+    <col min="18" max="18" width="41.85546875" style="31" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" style="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9" style="31" customWidth="1"/>
+    <col min="26" max="26" width="8.28515625" style="31" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -1948,52 +2041,58 @@
       <c r="Q1" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="S1" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="T1" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="U1" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="V1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="W1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="29" t="s">
+      <c r="X1" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="X1" s="19" t="s">
+      <c r="Y1" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="Y1" s="19" t="s">
+      <c r="Z1" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA1" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="Z1" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA1" s="23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB1" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC1" s="19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35">
         <v>2</v>
       </c>
       <c r="B2" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="C2" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="D2" s="58" t="s">
+      <c r="E2" s="59" t="s">
         <v>192</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>193</v>
       </c>
       <c r="F2" s="60" t="s">
         <v>83</v>
@@ -2030,62 +2129,67 @@
         <v>Data</v>
       </c>
       <c r="P2" s="62" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q2" s="62" t="s">
         <v>194</v>
       </c>
-      <c r="Q2" s="62" t="s">
-        <v>195</v>
-      </c>
       <c r="R2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="24" t="str">
-        <f t="shared" ref="S2:U14" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>202</v>
+      </c>
+      <c r="S2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="24" t="str">
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, ".", " ")</f>
         <v>De Tempo</v>
       </c>
-      <c r="T2" s="24" t="str">
+      <c r="U2" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Eventos</v>
       </c>
-      <c r="U2" s="24" t="str">
+      <c r="V2" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Calendários</v>
       </c>
-      <c r="V2" s="34" t="s">
+      <c r="W2" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W2" s="30" t="str">
+      <c r="X2" s="30" t="str">
         <f>CONCATENATE("Key-UAS-",A2)</f>
         <v>Key-UAS-2</v>
       </c>
-      <c r="X2" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y2" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z2" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="24" t="str">
-        <f>_xlfn.TRANSLATE(Q2,"es","en")</f>
-        <v>A calendar date for an event that happened or will happen.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA2" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB2" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC2" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>3</v>
       </c>
       <c r="B3" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C3" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D3" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E3" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" s="63" t="s">
         <v>80</v>
@@ -2122,66 +2226,70 @@
         <v>Drone</v>
       </c>
       <c r="P3" s="34" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q3" s="24" t="str">
-        <f t="shared" ref="Q3" si="3">_xlfn.TRANSLATE(P3,"pt","es")</f>
-        <v>Es una aeronave estándar de tipo dron o UAS.</v>
+        <v>105</v>
+      </c>
+      <c r="Q3" s="24" t="s">
+        <v>215</v>
       </c>
       <c r="R3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="24" t="str">
+        <v>203</v>
+      </c>
+      <c r="S3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T3" s="24" t="str">
+      <c r="U3" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U3" s="24" t="str">
+      <c r="V3" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Vistorias</v>
       </c>
-      <c r="V3" s="34" t="s">
+      <c r="W3" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W3" s="30" t="str">
-        <f t="shared" ref="W3:W14" si="4">CONCATENATE("Key-UAS-",A3)</f>
+      <c r="X3" s="30" t="str">
+        <f t="shared" ref="X3:X14" si="3">CONCATENATE("Key-UAS-",A3)</f>
         <v>Key-UAS-3</v>
       </c>
-      <c r="X3" s="24" t="s">
+      <c r="Y3" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z3" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA3" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="Y3" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA3" s="24" t="str">
-        <f>_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>It is a standard drone-type aircraft or UAS.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB3" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC3" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>4</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C4" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E4" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F4" s="63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>9</v>
@@ -2215,63 +2323,67 @@
         <v>Drone.LIDAR</v>
       </c>
       <c r="P4" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q4" s="24" t="str">
-        <f t="shared" ref="Q4:Q10" si="5">_xlfn.TRANSLATE(P4,"pt","es")</f>
-        <v>Es una aeronave tipo dron o UAS con un dispositivo LIDAR (Detección y Alcance de Luz) incorporado.</v>
+        <v>181</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>216</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="24" t="str">
+        <v>204</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T4" s="24" t="str">
+      <c r="U4" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U4" s="24" t="str">
+      <c r="V4" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Vistorias</v>
       </c>
-      <c r="V4" s="34" t="s">
+      <c r="W4" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W4" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X4" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-4</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="Y4" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="Y4" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA4" s="24" t="str">
-        <f>_xlfn.TRANSLATE(P4,"pt","en")</f>
-        <v>It is a drone-type aircraft or UAS with a built-in LIDAR (Light Detection and Ranging) device.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB4" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>5</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D5" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E5" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F5" s="63" t="s">
         <v>84</v>
@@ -2310,61 +2422,65 @@
       <c r="P5" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="Q5" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Plan de vuelo autónomo.</v>
+      <c r="Q5" s="24" t="s">
+        <v>217</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="24" t="str">
+        <v>205</v>
+      </c>
+      <c r="S5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T5" s="24" t="str">
+      <c r="U5" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U5" s="24" t="str">
+      <c r="V5" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Vistorias</v>
       </c>
-      <c r="V5" s="34" t="s">
+      <c r="W5" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W5" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X5" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-5</v>
       </c>
-      <c r="X5" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y5" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z5" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="24" t="str">
-        <f t="shared" ref="AA5:AA10" si="6">_xlfn.TRANSLATE(P5,"pt","en")</f>
-        <v>Autonomous flight plan.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA5" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB5" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC5" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>6</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D6" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E6" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F6" s="63" t="s">
         <v>76</v>
@@ -2403,61 +2519,65 @@
       <c r="P6" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="Q6" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Vuelo autónomo realizado con un dron.</v>
+      <c r="Q6" s="24" t="s">
+        <v>218</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="24" t="str">
+        <v>206</v>
+      </c>
+      <c r="S6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T6" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T6" s="24" t="str">
+      <c r="U6" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U6" s="24" t="str">
+      <c r="V6" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Vistorias</v>
       </c>
-      <c r="V6" s="34" t="s">
+      <c r="W6" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W6" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X6" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-6</v>
       </c>
-      <c r="X6" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y6" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z6" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v>Autonomous flight carried out with a drone.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA6" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB6" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC6" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>7</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C7" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D7" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E7" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F7" s="63" t="s">
         <v>77</v>
@@ -2496,61 +2616,65 @@
       <c r="P7" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="Q7" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>El vuelo manual se realiza con dron.</v>
+      <c r="Q7" s="24" t="s">
+        <v>219</v>
       </c>
       <c r="R7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="24" t="str">
+        <v>207</v>
+      </c>
+      <c r="S7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T7" s="24" t="str">
+      <c r="U7" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U7" s="24" t="str">
+      <c r="V7" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Vistorias</v>
       </c>
-      <c r="V7" s="34" t="s">
+      <c r="W7" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W7" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X7" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-7</v>
       </c>
-      <c r="X7" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y7" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z7" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v>Manual flight carried out with drone.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA7" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC7" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>8</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D8" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E8" s="63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F8" s="63" t="s">
         <v>78</v>
@@ -2589,64 +2713,68 @@
       <c r="P8" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="Q8" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Inspección realizada en el terreno.</v>
+      <c r="Q8" s="24" t="s">
+        <v>220</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="24" t="str">
+        <v>208</v>
+      </c>
+      <c r="S8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T8" s="24" t="str">
+      <c r="U8" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U8" s="24" t="str">
+      <c r="V8" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Vistorias</v>
       </c>
-      <c r="V8" s="34" t="s">
+      <c r="W8" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W8" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X8" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-8</v>
       </c>
-      <c r="X8" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y8" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z8" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v>Inspection carried out in the field.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA8" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC8" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>9</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C9" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D9" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E9" s="63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F9" s="63" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>9</v>
@@ -2680,66 +2808,70 @@
         <v>Imagem.Banco</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q9" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Banco de Imágenes Fotográficas correspondiente a un vuelo de mantenimiento realizado.</v>
+        <v>177</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>221</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="24" t="str">
+        <v>209</v>
+      </c>
+      <c r="S9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T9" s="24" t="str">
+      <c r="U9" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U9" s="24" t="str">
+      <c r="V9" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Imagens</v>
       </c>
-      <c r="V9" s="34" t="s">
+      <c r="W9" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W9" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X9" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-9</v>
       </c>
-      <c r="X9" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y9" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z9" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA9" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v>Photographic Image Bank corresponding to a Maintenance Flight performed.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA9" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB9" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC9" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>10</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D10" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E10" s="63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F10" s="63" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>9</v>
@@ -2773,66 +2905,70 @@
         <v>Imagem.WayPoint</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q10" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Imagen fotográfica correspondiente a un WayPoint.</v>
+        <v>155</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>222</v>
       </c>
       <c r="R10" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="24" t="str">
+        <v>210</v>
+      </c>
+      <c r="S10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T10" s="24" t="str">
+      <c r="U10" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U10" s="24" t="str">
+      <c r="V10" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Imagens</v>
       </c>
-      <c r="V10" s="34" t="s">
+      <c r="W10" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W10" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X10" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-10</v>
       </c>
-      <c r="X10" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y10" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z10" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="AA10" s="24" t="str">
-        <f t="shared" si="6"/>
-        <v>Photographic image corresponding to a WayPoint.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA10" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB10" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC10" s="24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>11</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C11" s="63" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D11" s="63" t="s">
         <v>75</v>
       </c>
       <c r="E11" s="63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11" s="63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>9</v>
@@ -2866,66 +3002,70 @@
         <v>Vídeo.Voo</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q11" s="24" t="str">
-        <f t="shared" ref="Q11" si="7">_xlfn.TRANSLATE(P11,"pt","es")</f>
-        <v>Vídeo grabado durante un vuelo.</v>
+        <v>180</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>223</v>
       </c>
       <c r="R11" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="24" t="str">
+        <v>211</v>
+      </c>
+      <c r="S11" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Operação</v>
       </c>
-      <c r="T11" s="24" t="str">
+      <c r="U11" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Manutenção</v>
       </c>
-      <c r="U11" s="24" t="str">
+      <c r="V11" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Imagens</v>
       </c>
-      <c r="V11" s="34" t="s">
+      <c r="W11" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W11" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X11" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-11</v>
       </c>
-      <c r="X11" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y11" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z11" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA11" s="24" t="str">
-        <f t="shared" ref="AA11" si="8">_xlfn.TRANSLATE(P11,"pt","en")</f>
-        <v>Video recorded during a flight.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA11" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB11" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC11" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>12</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D12" s="64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E12" s="64" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F12" s="63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G12" s="32" t="s">
         <v>9</v>
@@ -2959,66 +3099,70 @@
         <v>Voo.Preventivo</v>
       </c>
       <c r="P12" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q12" s="24" t="str">
-        <f t="shared" ref="Q12:Q14" si="9">_xlfn.TRANSLATE(P12,"pt","es")</f>
-        <v>El vuelo con drones planeó realizar acciones de conservación de los sistemas del edificio.</v>
+        <v>187</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>224</v>
       </c>
       <c r="R12" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="24" t="str">
+        <v>212</v>
+      </c>
+      <c r="S12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Manutenção</v>
       </c>
-      <c r="T12" s="24" t="str">
+      <c r="U12" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Diagnósticas</v>
       </c>
-      <c r="U12" s="24" t="str">
+      <c r="V12" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Preventivas</v>
       </c>
-      <c r="V12" s="34" t="s">
+      <c r="W12" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W12" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X12" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-12</v>
       </c>
-      <c r="X12" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y12" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z12" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA12" s="24" t="str">
-        <f t="shared" ref="AA12:AA14" si="10">_xlfn.TRANSLATE(P12,"pt","en")</f>
-        <v>Drone flight planned to take conservation actions of building systems.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA12" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB12" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC12" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>13</v>
       </c>
       <c r="B13" s="57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" s="64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E13" s="64" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F13" s="63" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G13" s="32" t="s">
         <v>9</v>
@@ -3052,66 +3196,70 @@
         <v>Voo.Corretivo</v>
       </c>
       <c r="P13" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q13" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v>El vuelo de drones planeó tomar medidas correctivas para patologías.</v>
+        <v>186</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>225</v>
       </c>
       <c r="R13" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="24" t="str">
+        <v>213</v>
+      </c>
+      <c r="S13" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T13" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Manutenção</v>
       </c>
-      <c r="T13" s="24" t="str">
+      <c r="U13" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Diagnósticas</v>
       </c>
-      <c r="U13" s="24" t="str">
+      <c r="V13" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Corretivas</v>
       </c>
-      <c r="V13" s="34" t="s">
+      <c r="W13" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W13" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X13" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-13</v>
       </c>
-      <c r="X13" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y13" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z13" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA13" s="24" t="str">
-        <f t="shared" si="10"/>
-        <v>Drone flight planned to take corrective actions for pathologies.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>227</v>
+      </c>
+      <c r="AA13" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB13" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC13" s="24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>14</v>
       </c>
       <c r="B14" s="57" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C14" s="64" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D14" s="64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E14" s="64" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F14" s="63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>9</v>
@@ -3145,83 +3293,91 @@
         <v>Voo.Preditivo</v>
       </c>
       <c r="P14" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q14" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v>Vuelo planificado con dron para predecir el mantenimiento futuro o patologías.</v>
+        <v>189</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>226</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S14" s="24" t="str">
+        <v>214</v>
+      </c>
+      <c r="S14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T14" s="24" t="str">
         <f t="shared" si="2"/>
         <v>De Manutenção</v>
       </c>
-      <c r="T14" s="24" t="str">
+      <c r="U14" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Diagnósticas</v>
       </c>
-      <c r="U14" s="24" t="str">
+      <c r="V14" s="24" t="str">
         <f t="shared" si="2"/>
         <v>Preditivas</v>
       </c>
-      <c r="V14" s="34" t="s">
+      <c r="W14" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="W14" s="30" t="str">
-        <f t="shared" si="4"/>
+      <c r="X14" s="30" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-14</v>
       </c>
-      <c r="X14" s="24" t="s">
-        <v>9</v>
-      </c>
       <c r="Y14" s="24" t="s">
         <v>9</v>
       </c>
       <c r="Z14" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA14" s="24" t="str">
-        <f t="shared" si="10"/>
-        <v>Planned drone flight to predict future maintenance or pathologies.</v>
+        <v>227</v>
+      </c>
+      <c r="AA14" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB14" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="AC14" s="24" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="12" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F7 F1">
-    <cfRule type="duplicateValues" dxfId="5" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12:F1048576 F1 F3:F7">
-    <cfRule type="duplicateValues" dxfId="3" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="2" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="39" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA14 A2:B14">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B14">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R14">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
     <ignoredError sqref="A1" numberStoredAsText="1"/>
-    <ignoredError sqref="AA2" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3230,14 +3386,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.69140625" style="12"/>
-    <col min="11" max="16384" width="5.69140625" style="16"/>
+    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.7109375" style="12"/>
+    <col min="11" max="16384" width="5.7109375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3302,7 +3458,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -3376,16 +3532,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.84375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.69140625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.3828125" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.15234375" style="13"/>
+    <col min="2" max="2" width="7.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -3399,7 +3555,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3421,126 +3577,126 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72143BD-9EBA-4CBF-96E5-A46CFFC881A3}">
   <dimension ref="A1:AA29"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.53515625" customWidth="1"/>
-    <col min="3" max="3" width="8.69140625" customWidth="1"/>
-    <col min="4" max="4" width="7.15234375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.84375" customWidth="1"/>
-    <col min="7" max="7" width="4.84375" customWidth="1"/>
-    <col min="8" max="8" width="7.15234375" customWidth="1"/>
-    <col min="9" max="9" width="7.3046875" customWidth="1"/>
-    <col min="10" max="10" width="3.69140625" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="7" max="7" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="3.15234375" customWidth="1"/>
-    <col min="13" max="13" width="14.53515625" customWidth="1"/>
-    <col min="14" max="14" width="4.53515625" customWidth="1"/>
-    <col min="15" max="15" width="7.15234375" customWidth="1"/>
-    <col min="16" max="16" width="5.3828125" customWidth="1"/>
-    <col min="17" max="17" width="28.84375" customWidth="1"/>
-    <col min="18" max="18" width="6.3828125" customWidth="1"/>
-    <col min="19" max="19" width="31.84375" customWidth="1"/>
-    <col min="20" max="20" width="2.84375" customWidth="1"/>
-    <col min="21" max="21" width="7.3046875" customWidth="1"/>
-    <col min="22" max="22" width="6.69140625" customWidth="1"/>
-    <col min="23" max="23" width="9.53515625" customWidth="1"/>
-    <col min="24" max="24" width="4.84375" customWidth="1"/>
-    <col min="25" max="25" width="7.3828125" customWidth="1"/>
-    <col min="26" max="26" width="6.3046875" customWidth="1"/>
-    <col min="27" max="27" width="10.3828125" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="4.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="16" max="16" width="5.42578125" customWidth="1"/>
+    <col min="17" max="17" width="28.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" customWidth="1"/>
+    <col min="19" max="19" width="31.85546875" customWidth="1"/>
+    <col min="20" max="20" width="2.85546875" customWidth="1"/>
+    <col min="21" max="21" width="7.28515625" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" customWidth="1"/>
+    <col min="25" max="25" width="7.42578125" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="37" t="s">
         <v>108</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>109</v>
       </c>
       <c r="C1" s="37" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E1" s="37" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G1" s="38" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I1" s="37" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K1" s="38" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M1" s="37" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O1" s="37" t="s">
         <v>2</v>
       </c>
       <c r="P1" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q1" s="38" t="s">
         <v>2</v>
       </c>
       <c r="R1" s="38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S1" s="38" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="U1" s="37" t="s">
         <v>2</v>
       </c>
       <c r="V1" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="W1" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="W1" s="41" t="s">
-        <v>111</v>
-      </c>
       <c r="X1" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y1" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="Y1" s="41" t="s">
-        <v>111</v>
-      </c>
       <c r="Z1" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA1" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="AA1" s="41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="43">
         <v>2</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C2" s="45" t="s">
         <v>80</v>
@@ -3576,57 +3732,57 @@
         <v>9</v>
       </c>
       <c r="N2" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="O2" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="O2" s="52" t="s">
+      <c r="P2" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q2" s="52" t="s">
         <v>129</v>
       </c>
-      <c r="P2" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q2" s="52" t="s">
+      <c r="R2" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="W2" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="R2" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="53" t="s">
+      <c r="X2" s="48" t="s">
         <v>118</v>
       </c>
-      <c r="W2" s="55" t="s">
+      <c r="Y2" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="X2" s="48" t="s">
+      <c r="Z2" s="48" t="s">
         <v>119</v>
       </c>
-      <c r="Y2" s="52" t="s">
+      <c r="AA2" s="52" t="s">
         <v>132</v>
       </c>
-      <c r="Z2" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA2" s="52" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43">
         <v>3</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D3" s="46" t="s">
         <v>9</v>
@@ -3653,22 +3809,22 @@
         <v>9</v>
       </c>
       <c r="L3" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="M3" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="M3" s="49" t="s">
+      <c r="N3" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="51" t="s">
         <v>113</v>
       </c>
-      <c r="N3" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="51" t="s">
-        <v>114</v>
-      </c>
       <c r="Q3" s="52" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R3" s="48" t="s">
         <v>9</v>
@@ -3695,39 +3851,39 @@
         <v>9</v>
       </c>
       <c r="Z3" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA3" s="52" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="43">
         <v>4</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D4" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="E4" s="54" t="s">
+      <c r="F4" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="F4" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="46" t="s">
-        <v>117</v>
-      </c>
       <c r="I4" s="54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J4" s="46" t="s">
         <v>9</v>
@@ -3748,10 +3904,10 @@
         <v>9</v>
       </c>
       <c r="P4" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q4" s="52" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R4" s="48" t="s">
         <v>9</v>
@@ -3778,27 +3934,27 @@
         <v>9</v>
       </c>
       <c r="Z4" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA4" s="52" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43">
         <v>5</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>9</v>
@@ -3807,10 +3963,10 @@
         <v>9</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I5" s="54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J5" s="46" t="s">
         <v>9</v>
@@ -3831,10 +3987,10 @@
         <v>9</v>
       </c>
       <c r="P5" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q5" s="52" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R5" s="48" t="s">
         <v>9</v>
@@ -3861,64 +4017,64 @@
         <v>9</v>
       </c>
       <c r="Z5" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA5" s="52" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43">
         <v>6</v>
       </c>
       <c r="B6" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="I6" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="J6" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="M6" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I6" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="J6" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="M6" s="49" t="s">
+      <c r="N6" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q6" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="N6" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q6" s="52" t="s">
-        <v>124</v>
-      </c>
       <c r="R6" s="51" t="s">
         <v>9</v>
       </c>
@@ -3944,52 +4100,52 @@
         <v>9</v>
       </c>
       <c r="Z6" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA6" s="52" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>7</v>
       </c>
       <c r="B7" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="I7" s="54" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="M7" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I7" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="J7" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="M7" s="49" t="s">
-        <v>126</v>
-      </c>
       <c r="N7" s="51" t="s">
         <v>9</v>
       </c>
@@ -3997,10 +4153,10 @@
         <v>9</v>
       </c>
       <c r="P7" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R7" s="51" t="s">
         <v>9</v>
@@ -4027,104 +4183,104 @@
         <v>9</v>
       </c>
       <c r="Z7" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA7" s="52" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="43">
         <v>8</v>
       </c>
       <c r="B8" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="I8" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q8" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="R8" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="V8" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="W8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="X8" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA8" s="52" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="43">
+        <v>9</v>
+      </c>
+      <c r="B9" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I8" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="J8" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q8" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="R8" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="T8" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="U8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="V8" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="W8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="X8" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z8" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA8" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="43">
-        <v>9</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>159</v>
-      </c>
       <c r="C9" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D9" s="46" t="s">
         <v>9</v>
@@ -4139,10 +4295,10 @@
         <v>9</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I9" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J9" s="46" t="s">
         <v>9</v>
@@ -4163,10 +4319,10 @@
         <v>9</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R9" s="51" t="s">
         <v>9</v>
@@ -4193,21 +4349,21 @@
         <v>9</v>
       </c>
       <c r="Z9" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA9" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="43">
         <v>10</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D10" s="46" t="s">
         <v>9</v>
@@ -4222,10 +4378,10 @@
         <v>9</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J10" s="46" t="s">
         <v>9</v>
@@ -4246,10 +4402,10 @@
         <v>9</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R10" s="51" t="s">
         <v>9</v>
@@ -4276,21 +4432,21 @@
         <v>9</v>
       </c>
       <c r="Z10" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA10" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="43">
         <v>11</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D11" s="46" t="s">
         <v>9</v>
@@ -4305,10 +4461,10 @@
         <v>9</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I11" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J11" s="46" t="s">
         <v>9</v>
@@ -4329,10 +4485,10 @@
         <v>9</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R11" s="51" t="s">
         <v>9</v>
@@ -4359,21 +4515,21 @@
         <v>9</v>
       </c>
       <c r="Z11" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA11" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="43">
         <v>12</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D12" s="46" t="s">
         <v>9</v>
@@ -4388,10 +4544,10 @@
         <v>9</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I12" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J12" s="46" t="s">
         <v>9</v>
@@ -4412,10 +4568,10 @@
         <v>9</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R12" s="51" t="s">
         <v>9</v>
@@ -4442,21 +4598,21 @@
         <v>9</v>
       </c>
       <c r="Z12" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA12" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="43">
         <v>13</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D13" s="46" t="s">
         <v>9</v>
@@ -4471,10 +4627,10 @@
         <v>9</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I13" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J13" s="46" t="s">
         <v>9</v>
@@ -4495,10 +4651,10 @@
         <v>9</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R13" s="51" t="s">
         <v>9</v>
@@ -4525,21 +4681,21 @@
         <v>9</v>
       </c>
       <c r="Z13" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA13" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="43">
         <v>14</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D14" s="46" t="s">
         <v>9</v>
@@ -4554,10 +4710,10 @@
         <v>9</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I14" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J14" s="46" t="s">
         <v>9</v>
@@ -4578,10 +4734,10 @@
         <v>9</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R14" s="51" t="s">
         <v>9</v>
@@ -4608,21 +4764,21 @@
         <v>9</v>
       </c>
       <c r="Z14" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA14" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="43">
         <v>15</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D15" s="46" t="s">
         <v>9</v>
@@ -4637,10 +4793,10 @@
         <v>9</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I15" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J15" s="46" t="s">
         <v>9</v>
@@ -4661,10 +4817,10 @@
         <v>9</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R15" s="51" t="s">
         <v>9</v>
@@ -4691,21 +4847,21 @@
         <v>9</v>
       </c>
       <c r="Z15" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA15" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="43">
         <v>16</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D16" s="46" t="s">
         <v>9</v>
@@ -4720,10 +4876,10 @@
         <v>9</v>
       </c>
       <c r="H16" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I16" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J16" s="46" t="s">
         <v>9</v>
@@ -4744,10 +4900,10 @@
         <v>9</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R16" s="51" t="s">
         <v>9</v>
@@ -4774,21 +4930,21 @@
         <v>9</v>
       </c>
       <c r="Z16" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA16" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="43">
         <v>17</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D17" s="46" t="s">
         <v>9</v>
@@ -4803,10 +4959,10 @@
         <v>9</v>
       </c>
       <c r="H17" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I17" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J17" s="46" t="s">
         <v>9</v>
@@ -4827,10 +4983,10 @@
         <v>9</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R17" s="51" t="s">
         <v>9</v>
@@ -4857,21 +5013,21 @@
         <v>9</v>
       </c>
       <c r="Z17" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA17" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <v>18</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D18" s="46" t="s">
         <v>9</v>
@@ -4886,10 +5042,10 @@
         <v>9</v>
       </c>
       <c r="H18" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I18" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J18" s="46" t="s">
         <v>9</v>
@@ -4910,10 +5066,10 @@
         <v>9</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q18" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R18" s="51" t="s">
         <v>9</v>
@@ -4940,21 +5096,21 @@
         <v>9</v>
       </c>
       <c r="Z18" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA18" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="43">
         <v>19</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D19" s="46" t="s">
         <v>9</v>
@@ -4969,10 +5125,10 @@
         <v>9</v>
       </c>
       <c r="H19" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I19" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J19" s="46" t="s">
         <v>9</v>
@@ -4993,10 +5149,10 @@
         <v>9</v>
       </c>
       <c r="P19" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q19" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R19" s="51" t="s">
         <v>9</v>
@@ -5023,21 +5179,21 @@
         <v>9</v>
       </c>
       <c r="Z19" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA19" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="43">
         <v>20</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D20" s="46" t="s">
         <v>9</v>
@@ -5052,10 +5208,10 @@
         <v>9</v>
       </c>
       <c r="H20" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I20" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J20" s="46" t="s">
         <v>9</v>
@@ -5076,10 +5232,10 @@
         <v>9</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R20" s="51" t="s">
         <v>9</v>
@@ -5106,21 +5262,21 @@
         <v>9</v>
       </c>
       <c r="Z20" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA20" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="43">
         <v>21</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D21" s="46" t="s">
         <v>9</v>
@@ -5135,10 +5291,10 @@
         <v>9</v>
       </c>
       <c r="H21" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I21" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J21" s="46" t="s">
         <v>9</v>
@@ -5159,10 +5315,10 @@
         <v>9</v>
       </c>
       <c r="P21" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R21" s="51" t="s">
         <v>9</v>
@@ -5189,21 +5345,21 @@
         <v>9</v>
       </c>
       <c r="Z21" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA21" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="43">
         <v>22</v>
       </c>
       <c r="B22" s="44" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D22" s="46" t="s">
         <v>9</v>
@@ -5218,10 +5374,10 @@
         <v>9</v>
       </c>
       <c r="H22" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I22" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J22" s="46" t="s">
         <v>9</v>
@@ -5242,10 +5398,10 @@
         <v>9</v>
       </c>
       <c r="P22" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q22" s="52" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="R22" s="51" t="s">
         <v>9</v>
@@ -5272,64 +5428,64 @@
         <v>9</v>
       </c>
       <c r="Z22" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA22" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="43">
         <v>23</v>
       </c>
       <c r="B23" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C23" s="45" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="J23" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O23" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P23" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q23" s="52" t="s">
         <v>173</v>
       </c>
-      <c r="C23" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="D23" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I23" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="J23" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L23" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M23" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N23" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O23" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P23" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q23" s="52" t="s">
-        <v>174</v>
-      </c>
       <c r="R23" s="51" t="s">
         <v>9</v>
       </c>
@@ -5355,64 +5511,64 @@
         <v>9</v>
       </c>
       <c r="Z23" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA23" s="52" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="43">
         <v>24</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C24" s="45" t="s">
         <v>84</v>
       </c>
       <c r="D24" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K24" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M24" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="N24" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O24" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P24" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q24" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="E24" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F24" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="I24" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="J24" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K24" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L24" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M24" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N24" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O24" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P24" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q24" s="52" t="s">
-        <v>136</v>
-      </c>
       <c r="R24" s="51" t="s">
         <v>9</v>
       </c>
@@ -5438,64 +5594,64 @@
         <v>9</v>
       </c>
       <c r="Z24" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA24" s="52" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="43">
         <v>25</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C25" s="45" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K25" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M25" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="N25" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O25" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P25" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q25" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="E25" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F25" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="I25" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="J25" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K25" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L25" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M25" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N25" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O25" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P25" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q25" s="52" t="s">
-        <v>136</v>
-      </c>
       <c r="R25" s="51" t="s">
         <v>9</v>
       </c>
@@ -5521,18 +5677,18 @@
         <v>9</v>
       </c>
       <c r="Z25" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA25" s="52" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="43">
         <v>26</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C26" s="45" t="s">
         <v>83</v>
@@ -5550,10 +5706,10 @@
         <v>9</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I26" s="54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J26" s="46" t="s">
         <v>9</v>
@@ -5574,23 +5730,23 @@
         <v>9</v>
       </c>
       <c r="P26" s="51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q26" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="R26" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="R26" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="S26" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="T26" s="48" t="s">
+      <c r="U26" s="56" t="s">
         <v>139</v>
       </c>
-      <c r="U26" s="56" t="s">
-        <v>140</v>
-      </c>
       <c r="V26" s="48" t="s">
         <v>9</v>
       </c>
@@ -5604,18 +5760,18 @@
         <v>9</v>
       </c>
       <c r="Z26" s="48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA26" s="52" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="43">
         <v>27</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C27" s="45" t="s">
         <v>83</v>
@@ -5633,124 +5789,124 @@
         <v>9</v>
       </c>
       <c r="H27" s="46" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I27" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M27" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="N27" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O27" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P27" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q27" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="R27" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="S27" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="T27" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="U27" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="V27" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="W27" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="X27" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y27" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z27" s="48" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA27" s="52" t="s">
         <v>152</v>
       </c>
-      <c r="J27" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K27" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L27" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M27" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N27" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O27" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P27" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q27" s="52" t="s">
-        <v>138</v>
-      </c>
-      <c r="R27" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="S27" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="T27" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="U27" s="56" t="s">
-        <v>141</v>
-      </c>
-      <c r="V27" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="W27" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="X27" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y27" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z27" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA27" s="52" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43">
         <v>28</v>
       </c>
       <c r="B28" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="D28" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="D28" s="46" t="s">
+      <c r="E28" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="46" t="s">
+      <c r="G28" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="I28" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="J28" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="K28" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="L28" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M28" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="N28" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O28" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P28" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q28" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="G28" s="54" t="s">
-        <v>134</v>
-      </c>
-      <c r="H28" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I28" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="J28" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="K28" s="47" t="s">
-        <v>116</v>
-      </c>
-      <c r="L28" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M28" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N28" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O28" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P28" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q28" s="52" t="s">
+      <c r="R28" s="51" t="s">
         <v>145</v>
       </c>
-      <c r="R28" s="51" t="s">
+      <c r="S28" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="S28" s="52" t="s">
-        <v>147</v>
-      </c>
       <c r="T28" s="51" t="s">
         <v>9</v>
       </c>
@@ -5776,63 +5932,63 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="43">
         <v>29</v>
       </c>
       <c r="B29" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="F29" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="G29" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="I29" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="J29" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="K29" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="L29" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="M29" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="N29" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="O29" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="P29" s="51" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q29" s="52" t="s">
+        <v>144</v>
+      </c>
+      <c r="R29" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="S29" s="52" t="s">
         <v>148</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="D29" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" s="46" t="s">
-        <v>144</v>
-      </c>
-      <c r="G29" s="54" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="I29" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="J29" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="K29" s="47" t="s">
-        <v>121</v>
-      </c>
-      <c r="L29" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M29" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N29" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O29" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P29" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q29" s="52" t="s">
-        <v>145</v>
-      </c>
-      <c r="R29" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="S29" s="52" t="s">
-        <v>149</v>
       </c>
       <c r="T29" s="51" t="s">
         <v>9</v>

--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F48C74-B462-4BCF-87F3-CB6CD902F029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A86906E-A5EF-4731-B0A6-4F32727B92C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="238">
   <si>
     <t>Edição</t>
   </si>
@@ -764,6 +764,27 @@
   </si>
   <si>
     <t>Atributo Ifc</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
   </si>
 </sst>
 </file>
@@ -854,7 +875,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -975,6 +996,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE79D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1027,7 +1066,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1215,13 +1254,47 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1239,6 +1312,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1877,7 +1960,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46253.628990972225</v>
+        <v>46258.591026041664</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>96</v>
@@ -1959,7 +2042,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
@@ -2141,7 +2224,7 @@
         <v>9</v>
       </c>
       <c r="T2" s="24" t="str">
-        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <f t="shared" ref="T2:V15" si="2">SUBSTITUTE(C2, ".", " ")</f>
         <v>De Tempo</v>
       </c>
       <c r="U2" s="24" t="str">
@@ -2253,7 +2336,7 @@
         <v>89</v>
       </c>
       <c r="X3" s="30" t="str">
-        <f t="shared" ref="X3:X14" si="3">CONCATENATE("Key-UAS-",A3)</f>
+        <f t="shared" ref="X3:X15" si="3">CONCATENATE("Key-UAS-",A3)</f>
         <v>Key-UAS-3</v>
       </c>
       <c r="Y3" s="24" t="s">
@@ -3339,38 +3422,148 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="35">
+        <v>15</v>
+      </c>
+      <c r="B15" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="70" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>233</v>
+      </c>
+      <c r="F15" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="65" t="str">
+        <f t="shared" ref="L15:O15" si="4">SUBSTITUTE(CONCATENATE("", C15), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M15" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N15" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Macros</v>
+      </c>
+      <c r="O15" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P15" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q15" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="R15" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="S15" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T15" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>De API</v>
+      </c>
+      <c r="U15" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V15" s="66" t="str">
+        <f t="shared" si="2"/>
+        <v>Macros</v>
+      </c>
+      <c r="W15" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="X15" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-15</v>
+      </c>
+      <c r="Y15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="13" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F7 F1">
-    <cfRule type="duplicateValues" dxfId="6" priority="186"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F12:F1048576 F1 F3:F7">
-    <cfRule type="duplicateValues" dxfId="4" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="3" priority="39" operator="equal">
+  <conditionalFormatting sqref="A2:B14 A15">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B14">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="16" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2">
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F7 F1">
+    <cfRule type="duplicateValues" dxfId="9" priority="189"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F14 F1 F16:F1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F12:F14 F1 F3:F7 F16:F1048576">
+    <cfRule type="duplicateValues" dxfId="7" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:O1">
+    <cfRule type="cellIs" dxfId="6" priority="42" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R14">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R15">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -6018,7 +6211,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="181"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A86906E-A5EF-4731-B0A6-4F32727B92C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55EAD74-CFD4-4EE2-98C4-4F5E357AE154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -1278,41 +1278,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1438,6 +1404,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1757,15 +1741,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="13" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="13"/>
+    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.3046875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1776,7 +1760,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1787,7 +1771,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1798,7 +1782,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1809,7 +1793,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1821,7 +1805,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1833,7 +1817,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1844,7 +1828,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1855,7 +1839,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1866,7 +1850,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1877,7 +1861,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -1888,7 +1872,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1899,7 +1883,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1910,7 +1894,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1921,7 +1905,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1932,7 +1916,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -1943,7 +1927,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1954,19 +1938,19 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46258.591026041664</v>
+        <v>46264.563345601855</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1977,7 +1961,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1988,7 +1972,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -1999,7 +1983,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -2010,7 +1994,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -2022,7 +2006,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
         <v>94</v>
       </c>
@@ -2043,36 +2027,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC15"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="11" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="55.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="55.3828125" style="31" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="46" style="31" customWidth="1"/>
-    <col min="18" max="18" width="41.85546875" style="31" customWidth="1"/>
-    <col min="19" max="19" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="41.84375" style="31" customWidth="1"/>
+    <col min="19" max="19" width="4.3046875" style="31" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.3046875" style="31" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="9" style="31" customWidth="1"/>
-    <col min="26" max="26" width="8.28515625" style="31" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="31"/>
+    <col min="26" max="26" width="8.3046875" style="31" customWidth="1"/>
+    <col min="27" max="27" width="7.3828125" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.84375" style="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2161,7 +2145,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="2" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="35">
         <v>2</v>
       </c>
@@ -2258,7 +2242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="35">
         <v>3</v>
       </c>
@@ -2355,7 +2339,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="35">
         <v>4</v>
       </c>
@@ -2452,7 +2436,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="35">
         <v>5</v>
       </c>
@@ -2549,7 +2533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="35">
         <v>6</v>
       </c>
@@ -2646,7 +2630,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="35">
         <v>7</v>
       </c>
@@ -2743,7 +2727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="35">
         <v>8</v>
       </c>
@@ -2840,7 +2824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="35">
         <v>9</v>
       </c>
@@ -2937,7 +2921,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="35">
         <v>10</v>
       </c>
@@ -3034,7 +3018,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="35">
         <v>11</v>
       </c>
@@ -3131,7 +3115,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="35">
         <v>12</v>
       </c>
@@ -3228,7 +3212,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="35">
         <v>13</v>
       </c>
@@ -3325,7 +3309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="35">
         <v>14</v>
       </c>
@@ -3422,7 +3406,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="35">
         <v>15</v>
       </c>
@@ -3433,10 +3417,10 @@
         <v>231</v>
       </c>
       <c r="D15" s="70" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" s="70" t="s">
         <v>232</v>
-      </c>
-      <c r="E15" s="70" t="s">
-        <v>233</v>
       </c>
       <c r="F15" s="70" t="s">
         <v>234</v>
@@ -3462,11 +3446,11 @@
       </c>
       <c r="M15" s="65" t="str">
         <f t="shared" si="4"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N15" s="65" t="str">
         <f t="shared" si="4"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O15" s="65" t="str">
         <f t="shared" si="4"/>
@@ -3490,11 +3474,11 @@
       </c>
       <c r="U15" s="24" t="str">
         <f t="shared" si="2"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V15" s="66" t="str">
         <f t="shared" si="2"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W15" s="34" t="s">
         <v>89</v>
@@ -3520,50 +3504,40 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B14 A15">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B15">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="16" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F7 F1">
-    <cfRule type="duplicateValues" dxfId="9" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="189"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F14 F1 F16:F1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12:F14 F1 F3:F7 F16:F1048576">
-    <cfRule type="duplicateValues" dxfId="7" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="6" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="42" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R15">
+  <conditionalFormatting sqref="R1:R15">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -3579,14 +3553,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.7109375" style="12"/>
-    <col min="11" max="16384" width="5.7109375" style="16"/>
+    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.69140625" style="12"/>
+    <col min="11" max="16384" width="5.69140625" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3651,7 +3625,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -3725,16 +3699,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="13"/>
+    <col min="2" max="2" width="7.84375" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.69140625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.3828125" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -3748,7 +3722,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3770,38 +3744,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72143BD-9EBA-4CBF-96E5-A46CFFC881A3}">
   <dimension ref="A1:AA29"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="7.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.53515625" customWidth="1"/>
+    <col min="3" max="3" width="8.69140625" customWidth="1"/>
+    <col min="4" max="4" width="7.15234375" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="7" width="4.85546875" customWidth="1"/>
-    <col min="8" max="8" width="7.140625" customWidth="1"/>
-    <col min="9" max="9" width="7.28515625" customWidth="1"/>
-    <col min="10" max="10" width="3.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.84375" customWidth="1"/>
+    <col min="7" max="7" width="4.84375" customWidth="1"/>
+    <col min="8" max="8" width="7.15234375" customWidth="1"/>
+    <col min="9" max="9" width="7.3046875" customWidth="1"/>
+    <col min="10" max="10" width="3.69140625" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="3.140625" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="4.5703125" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" customWidth="1"/>
-    <col min="16" max="16" width="5.42578125" customWidth="1"/>
-    <col min="17" max="17" width="28.85546875" customWidth="1"/>
-    <col min="18" max="18" width="6.42578125" customWidth="1"/>
-    <col min="19" max="19" width="31.85546875" customWidth="1"/>
-    <col min="20" max="20" width="2.85546875" customWidth="1"/>
-    <col min="21" max="21" width="7.28515625" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" customWidth="1"/>
-    <col min="23" max="23" width="9.5703125" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" customWidth="1"/>
-    <col min="25" max="25" width="7.42578125" customWidth="1"/>
-    <col min="26" max="26" width="6.28515625" customWidth="1"/>
-    <col min="27" max="27" width="10.42578125" customWidth="1"/>
+    <col min="12" max="12" width="3.15234375" customWidth="1"/>
+    <col min="13" max="13" width="14.53515625" customWidth="1"/>
+    <col min="14" max="14" width="4.53515625" customWidth="1"/>
+    <col min="15" max="15" width="7.15234375" customWidth="1"/>
+    <col min="16" max="16" width="5.3828125" customWidth="1"/>
+    <col min="17" max="17" width="28.84375" customWidth="1"/>
+    <col min="18" max="18" width="6.3828125" customWidth="1"/>
+    <col min="19" max="19" width="31.84375" customWidth="1"/>
+    <col min="20" max="20" width="2.84375" customWidth="1"/>
+    <col min="21" max="21" width="7.3046875" customWidth="1"/>
+    <col min="22" max="22" width="6.69140625" customWidth="1"/>
+    <col min="23" max="23" width="9.53515625" customWidth="1"/>
+    <col min="24" max="24" width="4.84375" customWidth="1"/>
+    <col min="25" max="25" width="7.3828125" customWidth="1"/>
+    <col min="26" max="26" width="6.3046875" customWidth="1"/>
+    <col min="27" max="27" width="10.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="36" t="s">
         <v>107</v>
       </c>
@@ -3884,7 +3858,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -3967,7 +3941,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -4050,7 +4024,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -4133,7 +4107,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -4216,7 +4190,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -4299,7 +4273,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -4382,7 +4356,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -4465,7 +4439,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -4548,7 +4522,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -4631,7 +4605,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -4714,7 +4688,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -4797,7 +4771,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -4880,7 +4854,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -4963,7 +4937,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -5046,7 +5020,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -5129,7 +5103,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -5212,7 +5186,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -5295,7 +5269,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -5378,7 +5352,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -5461,7 +5435,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -5544,7 +5518,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -5627,7 +5601,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -5710,7 +5684,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -5793,7 +5767,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -5876,7 +5850,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -5959,7 +5933,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -6042,7 +6016,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -6125,7 +6099,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -6211,7 +6185,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B29">
-    <cfRule type="duplicateValues" dxfId="4" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55EAD74-CFD4-4EE2-98C4-4F5E357AE154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC4F1CC-D788-410B-B780-6D3B4C3D1EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="254">
   <si>
     <t>Edição</t>
   </si>
@@ -754,9 +754,6 @@
     <t>Vuelo planificado con dron para predecir el mantenimiento futuro o patologías.</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parâmetro Rvt</t>
   </si>
   <si>
@@ -775,16 +772,67 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
   </si>
 </sst>
 </file>
@@ -875,7 +923,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1008,12 +1056,6 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1066,7 +1108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1268,17 +1310,47 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1414,14 +1486,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1741,15 +1805,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.3046875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="13"/>
+    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1760,7 +1824,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1771,7 +1835,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -1782,7 +1846,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1793,7 +1857,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1805,7 +1869,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1817,7 +1881,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -1828,7 +1892,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1839,7 +1903,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1850,7 +1914,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1861,7 +1925,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
@@ -1872,7 +1936,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
@@ -1883,7 +1947,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1894,7 +1958,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -1905,7 +1969,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1916,7 +1980,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
@@ -1927,7 +1991,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
@@ -1938,19 +2002,19 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46264.563345601855</v>
+        <v>46268.514778472221</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1961,7 +2025,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1972,7 +2036,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -1983,7 +2047,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -1994,7 +2058,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>29</v>
       </c>
@@ -2006,7 +2070,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>94</v>
       </c>
@@ -2026,37 +2090,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC15"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC19"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" style="31" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="31" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="55.3828125" style="31" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="46" style="31" customWidth="1"/>
-    <col min="18" max="18" width="41.84375" style="31" customWidth="1"/>
-    <col min="19" max="19" width="4.3046875" style="31" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="43.42578125" style="31" customWidth="1"/>
+    <col min="17" max="17" width="42.42578125" style="31" customWidth="1"/>
+    <col min="18" max="18" width="37.85546875" style="31" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.69140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.15234375" style="31" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.3046875" style="31" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9" style="31" customWidth="1"/>
-    <col min="26" max="26" width="8.3046875" style="31" customWidth="1"/>
-    <col min="27" max="27" width="7.3828125" style="31" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.53515625" style="31" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.84375" style="31" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="31"/>
+    <col min="21" max="21" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.140625" style="31" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9" style="31" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.85546875" style="31" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2133,19 +2198,19 @@
         <v>90</v>
       </c>
       <c r="Z1" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AA1" s="19" t="s">
         <v>91</v>
       </c>
       <c r="AB1" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AC1" s="19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35">
         <v>2</v>
       </c>
@@ -2208,7 +2273,7 @@
         <v>9</v>
       </c>
       <c r="T2" s="24" t="str">
-        <f t="shared" ref="T2:V15" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <f t="shared" ref="T2:V17" si="2">SUBSTITUTE(C2, ".", " ")</f>
         <v>De Tempo</v>
       </c>
       <c r="U2" s="24" t="str">
@@ -2229,20 +2294,20 @@
       <c r="Y2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="24" t="s">
-        <v>227</v>
+      <c r="Z2" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="24" t="s">
-        <v>227</v>
+      <c r="AB2" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>3</v>
       </c>
@@ -2320,26 +2385,26 @@
         <v>89</v>
       </c>
       <c r="X3" s="30" t="str">
-        <f t="shared" ref="X3:X15" si="3">CONCATENATE("Key-UAS-",A3)</f>
+        <f t="shared" ref="X3:X19" si="3">CONCATENATE("Key-UAS-",A3)</f>
         <v>Key-UAS-3</v>
       </c>
       <c r="Y3" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="Z3" s="24" t="s">
-        <v>227</v>
+      <c r="Z3" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="AB3" s="24" t="s">
-        <v>227</v>
+      <c r="AB3" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="24" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>4</v>
       </c>
@@ -2423,20 +2488,20 @@
       <c r="Y4" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="Z4" s="24" t="s">
-        <v>227</v>
+      <c r="Z4" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="AB4" s="24" t="s">
-        <v>227</v>
+      <c r="AB4" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="24" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>5</v>
       </c>
@@ -2520,20 +2585,20 @@
       <c r="Y5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="24" t="s">
-        <v>227</v>
+      <c r="Z5" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB5" s="24" t="s">
-        <v>227</v>
+      <c r="AB5" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>6</v>
       </c>
@@ -2617,20 +2682,20 @@
       <c r="Y6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="24" t="s">
-        <v>227</v>
+      <c r="Z6" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB6" s="24" t="s">
-        <v>227</v>
+      <c r="AB6" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>7</v>
       </c>
@@ -2714,20 +2779,20 @@
       <c r="Y7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z7" s="24" t="s">
-        <v>227</v>
+      <c r="Z7" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB7" s="24" t="s">
-        <v>227</v>
+      <c r="AB7" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>8</v>
       </c>
@@ -2811,20 +2876,20 @@
       <c r="Y8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z8" s="24" t="s">
-        <v>227</v>
+      <c r="Z8" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB8" s="24" t="s">
-        <v>227</v>
+      <c r="AB8" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>9</v>
       </c>
@@ -2908,20 +2973,20 @@
       <c r="Y9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z9" s="24" t="s">
-        <v>227</v>
+      <c r="Z9" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB9" s="24" t="s">
-        <v>227</v>
+      <c r="AB9" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="24" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>10</v>
       </c>
@@ -3005,20 +3070,20 @@
       <c r="Y10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z10" s="24" t="s">
-        <v>227</v>
+      <c r="Z10" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB10" s="24" t="s">
-        <v>227</v>
+      <c r="AB10" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="24" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>11</v>
       </c>
@@ -3102,20 +3167,20 @@
       <c r="Y11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z11" s="24" t="s">
-        <v>227</v>
+      <c r="Z11" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB11" s="24" t="s">
-        <v>227</v>
+      <c r="AB11" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="24" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>12</v>
       </c>
@@ -3199,20 +3264,20 @@
       <c r="Y12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z12" s="24" t="s">
-        <v>227</v>
+      <c r="Z12" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB12" s="24" t="s">
-        <v>227</v>
+      <c r="AB12" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>13</v>
       </c>
@@ -3296,20 +3361,20 @@
       <c r="Y13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z13" s="24" t="s">
-        <v>227</v>
+      <c r="Z13" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB13" s="24" t="s">
-        <v>227</v>
+      <c r="AB13" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>14</v>
       </c>
@@ -3393,38 +3458,38 @@
       <c r="Y14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z14" s="24" t="s">
-        <v>227</v>
+      <c r="Z14" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB14" s="24" t="s">
-        <v>227</v>
+      <c r="AB14" s="67" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="24" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="35">
         <v>15</v>
       </c>
-      <c r="B15" s="69" t="s">
+      <c r="B15" s="57" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="70" t="s">
+      <c r="C15" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" s="63" t="s">
         <v>231</v>
       </c>
-      <c r="D15" s="70" t="s">
+      <c r="F15" s="63" t="s">
         <v>233</v>
       </c>
-      <c r="E15" s="70" t="s">
-        <v>232</v>
-      </c>
-      <c r="F15" s="70" t="s">
-        <v>234</v>
-      </c>
       <c r="G15" s="32" t="s">
         <v>9</v>
       </c>
@@ -3441,7 +3506,7 @@
         <v>9</v>
       </c>
       <c r="L15" s="65" t="str">
-        <f t="shared" ref="L15:O15" si="4">SUBSTITUTE(CONCATENATE("", C15), ".", " ")</f>
+        <f t="shared" ref="L15:O19" si="4">SUBSTITUTE(CONCATENATE("", C15), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M15" s="65" t="str">
@@ -3454,16 +3519,16 @@
       </c>
       <c r="O15" s="65" t="str">
         <f t="shared" si="4"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P15" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q15" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="Q15" s="24" t="s">
+      <c r="R15" s="24" t="s">
         <v>236</v>
-      </c>
-      <c r="R15" s="24" t="s">
-        <v>237</v>
       </c>
       <c r="S15" s="24" t="s">
         <v>9</v>
@@ -3503,44 +3568,440 @@
         <v>9</v>
       </c>
     </row>
+    <row r="16" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="35">
+        <v>16</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>De API</v>
+      </c>
+      <c r="M16" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Macros</v>
+      </c>
+      <c r="N16" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O16" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P16" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q16" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="R16" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="S16" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>De API</v>
+      </c>
+      <c r="U16" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>Macros</v>
+      </c>
+      <c r="V16" s="66" t="str">
+        <f t="shared" si="2"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W16" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="X16" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-16</v>
+      </c>
+      <c r="Y16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="35">
+        <v>17</v>
+      </c>
+      <c r="B17" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>241</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>De API</v>
+      </c>
+      <c r="M17" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Macros</v>
+      </c>
+      <c r="N17" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O17" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P17" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="R17" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="S17" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>De API</v>
+      </c>
+      <c r="U17" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>Macros</v>
+      </c>
+      <c r="V17" s="66" t="str">
+        <f t="shared" si="2"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W17" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="X17" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-17</v>
+      </c>
+      <c r="Y17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB17" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="35">
+        <v>18</v>
+      </c>
+      <c r="B18" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>De API</v>
+      </c>
+      <c r="M18" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Macros</v>
+      </c>
+      <c r="N18" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O18" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P18" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="R18" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="S18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="24" t="str">
+        <f t="shared" ref="T18:V19" si="5">SUBSTITUTE(C18, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U18" s="24" t="str">
+        <f t="shared" si="5"/>
+        <v>Macros</v>
+      </c>
+      <c r="V18" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W18" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="X18" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-18</v>
+      </c>
+      <c r="Y18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="35">
+        <v>19</v>
+      </c>
+      <c r="B19" s="57" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>230</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>232</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>249</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>250</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>De API</v>
+      </c>
+      <c r="M19" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Macros</v>
+      </c>
+      <c r="N19" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O19" s="65" t="str">
+        <f t="shared" si="4"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P19" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q19" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="R19" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="S19" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="24" t="str">
+        <f t="shared" si="5"/>
+        <v>De API</v>
+      </c>
+      <c r="U19" s="24" t="str">
+        <f t="shared" si="5"/>
+        <v>Macros</v>
+      </c>
+      <c r="V19" s="66" t="str">
+        <f t="shared" si="5"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W19" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="X19" s="30" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-19</v>
+      </c>
+      <c r="Y19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B15">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B14 A15:A19">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="13" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F7 F1">
-    <cfRule type="duplicateValues" dxfId="6" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="192"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F14 F1 F16:F1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
+  <conditionalFormatting sqref="F3:F14 F1 F20:F1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F12:F14 F1 F3:F7 F16:F1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="40"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  <conditionalFormatting sqref="F12:F14 F1 F3:F7 F20:F1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="2" priority="42" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="45" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R15">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R14">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:B19">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:F19">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F18">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -3553,14 +4014,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.69140625" style="12"/>
-    <col min="11" max="16384" width="5.69140625" style="16"/>
+    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.7109375" style="12"/>
+    <col min="11" max="16384" width="5.7109375" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="14">
         <v>1</v>
       </c>
@@ -3625,7 +4086,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -3699,16 +4160,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.84375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.69140625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.3828125" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.15234375" style="13"/>
+    <col min="2" max="2" width="7.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -3722,7 +4183,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
@@ -3744,38 +4205,38 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72143BD-9EBA-4CBF-96E5-A46CFFC881A3}">
   <dimension ref="A1:AA29"/>
-  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.53515625" customWidth="1"/>
-    <col min="3" max="3" width="8.69140625" customWidth="1"/>
-    <col min="4" max="4" width="7.15234375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="6.84375" customWidth="1"/>
-    <col min="7" max="7" width="4.84375" customWidth="1"/>
-    <col min="8" max="8" width="7.15234375" customWidth="1"/>
-    <col min="9" max="9" width="7.3046875" customWidth="1"/>
-    <col min="10" max="10" width="3.69140625" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="7" max="7" width="4.85546875" customWidth="1"/>
+    <col min="8" max="8" width="7.140625" customWidth="1"/>
+    <col min="9" max="9" width="7.28515625" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" customWidth="1"/>
     <col min="11" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="3.15234375" customWidth="1"/>
-    <col min="13" max="13" width="14.53515625" customWidth="1"/>
-    <col min="14" max="14" width="4.53515625" customWidth="1"/>
-    <col min="15" max="15" width="7.15234375" customWidth="1"/>
-    <col min="16" max="16" width="5.3828125" customWidth="1"/>
-    <col min="17" max="17" width="28.84375" customWidth="1"/>
-    <col min="18" max="18" width="6.3828125" customWidth="1"/>
-    <col min="19" max="19" width="31.84375" customWidth="1"/>
-    <col min="20" max="20" width="2.84375" customWidth="1"/>
-    <col min="21" max="21" width="7.3046875" customWidth="1"/>
-    <col min="22" max="22" width="6.69140625" customWidth="1"/>
-    <col min="23" max="23" width="9.53515625" customWidth="1"/>
-    <col min="24" max="24" width="4.84375" customWidth="1"/>
-    <col min="25" max="25" width="7.3828125" customWidth="1"/>
-    <col min="26" max="26" width="6.3046875" customWidth="1"/>
-    <col min="27" max="27" width="10.3828125" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="4.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="16" max="16" width="5.42578125" customWidth="1"/>
+    <col min="17" max="17" width="28.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" customWidth="1"/>
+    <col min="19" max="19" width="31.85546875" customWidth="1"/>
+    <col min="20" max="20" width="2.85546875" customWidth="1"/>
+    <col min="21" max="21" width="7.28515625" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" customWidth="1"/>
+    <col min="25" max="25" width="7.42578125" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
         <v>107</v>
       </c>
@@ -3858,7 +4319,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="43">
         <v>2</v>
       </c>
@@ -3941,7 +4402,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="43">
         <v>3</v>
       </c>
@@ -4024,7 +4485,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="43">
         <v>4</v>
       </c>
@@ -4107,7 +4568,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="43">
         <v>5</v>
       </c>
@@ -4190,7 +4651,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43">
         <v>6</v>
       </c>
@@ -4273,7 +4734,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>7</v>
       </c>
@@ -4356,7 +4817,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="43">
         <v>8</v>
       </c>
@@ -4439,7 +4900,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="43">
         <v>9</v>
       </c>
@@ -4522,7 +4983,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="43">
         <v>10</v>
       </c>
@@ -4605,7 +5066,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="43">
         <v>11</v>
       </c>
@@ -4688,7 +5149,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="43">
         <v>12</v>
       </c>
@@ -4771,7 +5232,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="43">
         <v>13</v>
       </c>
@@ -4854,7 +5315,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="43">
         <v>14</v>
       </c>
@@ -4937,7 +5398,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="43">
         <v>15</v>
       </c>
@@ -5020,7 +5481,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="43">
         <v>16</v>
       </c>
@@ -5103,7 +5564,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="43">
         <v>17</v>
       </c>
@@ -5186,7 +5647,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="43">
         <v>18</v>
       </c>
@@ -5269,7 +5730,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="43">
         <v>19</v>
       </c>
@@ -5352,7 +5813,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="43">
         <v>20</v>
       </c>
@@ -5435,7 +5896,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="43">
         <v>21</v>
       </c>
@@ -5518,7 +5979,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="43">
         <v>22</v>
       </c>
@@ -5601,7 +6062,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="43">
         <v>23</v>
       </c>
@@ -5684,7 +6145,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="43">
         <v>24</v>
       </c>
@@ -5767,7 +6228,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="43">
         <v>25</v>
       </c>
@@ -5850,7 +6311,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="43">
         <v>26</v>
       </c>
@@ -5933,7 +6394,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="43">
         <v>27</v>
       </c>
@@ -6016,7 +6477,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="43">
         <v>28</v>
       </c>
@@ -6099,7 +6560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="43">
         <v>29</v>
       </c>
@@ -6185,7 +6646,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="181"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC4F1CC-D788-410B-B780-6D3B4C3D1EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEF79DF-A94A-4159-8301-2A827E2541AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="255">
   <si>
     <t>Edição</t>
   </si>
@@ -833,6 +833,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1314,43 +1317,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1486,6 +1453,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2008,7 +1993,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.514778472221</v>
+        <v>46268.68915914352</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>96</v>
@@ -2090,7 +2075,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
@@ -2118,10 +2103,11 @@
     <col min="27" max="27" width="7.42578125" style="31" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="9" style="31" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="9.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="31"/>
+    <col min="30" max="30" width="9" style="31" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>30</v>
       </c>
@@ -2209,8 +2195,11 @@
       <c r="AC1" s="19" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD1" s="19" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35">
         <v>2</v>
       </c>
@@ -2306,8 +2295,11 @@
       <c r="AC2" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD2" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="35">
         <v>3</v>
       </c>
@@ -2403,8 +2395,11 @@
       <c r="AC3" s="24" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD3" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>4</v>
       </c>
@@ -2500,8 +2495,11 @@
       <c r="AC4" s="24" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD4" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>5</v>
       </c>
@@ -2597,8 +2595,11 @@
       <c r="AC5" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD5" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>6</v>
       </c>
@@ -2694,8 +2695,11 @@
       <c r="AC6" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD6" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>7</v>
       </c>
@@ -2791,8 +2795,11 @@
       <c r="AC7" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD7" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>8</v>
       </c>
@@ -2888,8 +2895,11 @@
       <c r="AC8" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD8" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>9</v>
       </c>
@@ -2985,8 +2995,11 @@
       <c r="AC9" s="24" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD9" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>10</v>
       </c>
@@ -3082,8 +3095,11 @@
       <c r="AC10" s="24" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD10" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>11</v>
       </c>
@@ -3179,8 +3195,11 @@
       <c r="AC11" s="24" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD11" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>12</v>
       </c>
@@ -3276,8 +3295,11 @@
       <c r="AC12" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD12" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>13</v>
       </c>
@@ -3373,8 +3395,11 @@
       <c r="AC13" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD13" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>14</v>
       </c>
@@ -3470,8 +3495,11 @@
       <c r="AC14" s="24" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD14" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="35">
         <v>15</v>
       </c>
@@ -3567,8 +3595,11 @@
       <c r="AC15" s="67" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD15" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="35">
         <v>16</v>
       </c>
@@ -3664,8 +3695,11 @@
       <c r="AC16" s="67" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD16" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="35">
         <v>17</v>
       </c>
@@ -3761,8 +3795,11 @@
       <c r="AC17" s="67" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD17" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="35">
         <v>18</v>
       </c>
@@ -3858,8 +3895,11 @@
       <c r="AC18" s="67" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD18" s="67" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="35">
         <v>19</v>
       </c>
@@ -3955,53 +3995,51 @@
       <c r="AC19" s="67" t="s">
         <v>9</v>
       </c>
+      <c r="AD19" s="67" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B14 A15:A19">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:B19">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E19:F19">
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="17" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="12" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F7 F1">
-    <cfRule type="duplicateValues" dxfId="10" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="192"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F14 F1 F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12:F14 F1 F3:F7 F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F18">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="6" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="45" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B15:B19">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E19:F19">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F18">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -6646,7 +6684,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B29">
-    <cfRule type="duplicateValues" dxfId="4" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EEF79DF-A94A-4159-8301-2A827E2541AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992AFFD0-1846-4C2C-A889-50F8F0133D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="267">
   <si>
     <t>Edição</t>
   </si>
@@ -763,15 +763,6 @@
     <t>Atributo Ifc</t>
   </si>
   <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>Função.Auxiliar</t>
   </si>
   <si>
@@ -820,9 +811,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -836,6 +824,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -926,7 +962,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1059,6 +1095,12 @@
         <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1111,7 +1153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1277,30 +1319,12 @@
     <xf numFmtId="14" fontId="7" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1310,14 +1334,77 @@
     <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1463,14 +1550,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1993,7 +2072,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46268.68915914352</v>
+        <v>46273.517005208334</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>96</v>
@@ -2081,9 +2160,8 @@
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.28515625" style="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.140625" style="31" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="31" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" style="31" customWidth="1"/>
+    <col min="5" max="6" width="8.42578125" style="31" customWidth="1"/>
     <col min="7" max="11" width="10.140625" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" style="31" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
@@ -2092,9 +2170,9 @@
     <col min="16" max="16" width="43.42578125" style="31" customWidth="1"/>
     <col min="17" max="17" width="42.42578125" style="31" customWidth="1"/>
     <col min="18" max="18" width="37.85546875" style="31" customWidth="1"/>
-    <col min="19" max="19" width="4.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.28515625" style="65" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="31" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.28515625" style="31" customWidth="1"/>
     <col min="22" max="22" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="11.140625" style="31" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7.28515625" style="31" bestFit="1" customWidth="1"/>
@@ -2162,7 +2240,7 @@
       <c r="R1" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="S1" s="19" t="s">
+      <c r="S1" s="64" t="s">
         <v>71</v>
       </c>
       <c r="T1" s="19" t="s">
@@ -2196,69 +2274,69 @@
         <v>228</v>
       </c>
       <c r="AD1" s="19" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35">
         <v>2</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="67" t="s">
         <v>191</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="68" t="s">
         <v>192</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="62" t="str">
+      <c r="G2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="58" t="str">
         <f t="shared" ref="L2:L14" si="0">_xlfn.CONCAT(C2)</f>
         <v>De.Tempo</v>
       </c>
-      <c r="M2" s="62" t="str">
+      <c r="M2" s="58" t="str">
         <f t="shared" ref="M2:O14" si="1">_xlfn.CONCAT("", D2)</f>
         <v>Eventos</v>
       </c>
-      <c r="N2" s="62" t="str">
+      <c r="N2" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Calendários</v>
       </c>
-      <c r="O2" s="62" t="str">
+      <c r="O2" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Data</v>
       </c>
-      <c r="P2" s="62" t="s">
+      <c r="P2" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="Q2" s="62" t="s">
+      <c r="Q2" s="58" t="s">
         <v>194</v>
       </c>
       <c r="R2" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="S2" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T2" s="24" t="str">
@@ -2283,19 +2361,19 @@
       <c r="Y2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="67" t="s">
+      <c r="Z2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="67" t="s">
+      <c r="AB2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD2" s="67" t="s">
+      <c r="AD2" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2303,19 +2381,19 @@
       <c r="A3" s="35">
         <v>3</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C3" s="63" t="s">
+      <c r="C3" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E3" s="63" t="s">
+      <c r="E3" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="63" t="s">
+      <c r="F3" s="70" t="s">
         <v>80</v>
       </c>
       <c r="G3" s="32" t="s">
@@ -2333,19 +2411,19 @@
       <c r="K3" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="62" t="str">
+      <c r="L3" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M3" s="62" t="str">
+      <c r="M3" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N3" s="62" t="str">
+      <c r="N3" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Vistorias</v>
       </c>
-      <c r="O3" s="62" t="str">
+      <c r="O3" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Drone</v>
       </c>
@@ -2358,7 +2436,7 @@
       <c r="R3" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="S3" s="24" t="s">
+      <c r="S3" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T3" s="24" t="str">
@@ -2383,19 +2461,19 @@
       <c r="Y3" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="Z3" s="67" t="s">
+      <c r="Z3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="AB3" s="67" t="s">
+      <c r="AB3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="AD3" s="67" t="s">
+      <c r="AD3" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2403,19 +2481,19 @@
       <c r="A4" s="35">
         <v>4</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C4" s="63" t="s">
+      <c r="C4" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D4" s="63" t="s">
+      <c r="D4" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="63" t="s">
+      <c r="E4" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="63" t="s">
+      <c r="F4" s="70" t="s">
         <v>103</v>
       </c>
       <c r="G4" s="32" t="s">
@@ -2433,19 +2511,19 @@
       <c r="K4" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="62" t="str">
+      <c r="L4" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M4" s="62" t="str">
+      <c r="M4" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N4" s="62" t="str">
+      <c r="N4" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Vistorias</v>
       </c>
-      <c r="O4" s="62" t="str">
+      <c r="O4" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Drone.LIDAR</v>
       </c>
@@ -2458,7 +2536,7 @@
       <c r="R4" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="S4" s="24" t="s">
+      <c r="S4" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T4" s="24" t="str">
@@ -2483,19 +2561,19 @@
       <c r="Y4" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="Z4" s="67" t="s">
+      <c r="Z4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="AB4" s="67" t="s">
+      <c r="AB4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="AD4" s="67" t="s">
+      <c r="AD4" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2503,19 +2581,19 @@
       <c r="A5" s="35">
         <v>5</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="63" t="s">
+      <c r="E5" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="63" t="s">
+      <c r="F5" s="70" t="s">
         <v>84</v>
       </c>
       <c r="G5" s="32" t="s">
@@ -2533,19 +2611,19 @@
       <c r="K5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="62" t="str">
+      <c r="L5" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M5" s="62" t="str">
+      <c r="M5" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N5" s="62" t="str">
+      <c r="N5" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Vistorias</v>
       </c>
-      <c r="O5" s="62" t="str">
+      <c r="O5" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Voo.Plano</v>
       </c>
@@ -2558,7 +2636,7 @@
       <c r="R5" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S5" s="24" t="s">
+      <c r="S5" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T5" s="24" t="str">
@@ -2583,19 +2661,19 @@
       <c r="Y5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z5" s="67" t="s">
+      <c r="Z5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB5" s="67" t="s">
+      <c r="AB5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD5" s="67" t="s">
+      <c r="AD5" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2603,19 +2681,19 @@
       <c r="A6" s="35">
         <v>6</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F6" s="63" t="s">
+      <c r="F6" s="70" t="s">
         <v>76</v>
       </c>
       <c r="G6" s="32" t="s">
@@ -2633,19 +2711,19 @@
       <c r="K6" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="62" t="str">
+      <c r="L6" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M6" s="62" t="str">
+      <c r="M6" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N6" s="62" t="str">
+      <c r="N6" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Vistorias</v>
       </c>
-      <c r="O6" s="62" t="str">
+      <c r="O6" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Voo.Autônomo</v>
       </c>
@@ -2658,7 +2736,7 @@
       <c r="R6" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="S6" s="24" t="s">
+      <c r="S6" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T6" s="24" t="str">
@@ -2683,19 +2761,19 @@
       <c r="Y6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z6" s="67" t="s">
+      <c r="Z6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB6" s="67" t="s">
+      <c r="AB6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD6" s="67" t="s">
+      <c r="AD6" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2703,19 +2781,19 @@
       <c r="A7" s="35">
         <v>7</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="63" t="s">
+      <c r="E7" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F7" s="63" t="s">
+      <c r="F7" s="70" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="32" t="s">
@@ -2733,19 +2811,19 @@
       <c r="K7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L7" s="62" t="str">
+      <c r="L7" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M7" s="62" t="str">
+      <c r="M7" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N7" s="62" t="str">
+      <c r="N7" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Vistorias</v>
       </c>
-      <c r="O7" s="62" t="str">
+      <c r="O7" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Voo.Manual</v>
       </c>
@@ -2758,7 +2836,7 @@
       <c r="R7" s="24" t="s">
         <v>207</v>
       </c>
-      <c r="S7" s="24" t="s">
+      <c r="S7" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T7" s="24" t="str">
@@ -2783,19 +2861,19 @@
       <c r="Y7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z7" s="67" t="s">
+      <c r="Z7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB7" s="67" t="s">
+      <c r="AB7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD7" s="67" t="s">
+      <c r="AD7" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2803,19 +2881,19 @@
       <c r="A8" s="35">
         <v>8</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="63" t="s">
+      <c r="D8" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="63" t="s">
+      <c r="E8" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="F8" s="63" t="s">
+      <c r="F8" s="70" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="32" t="s">
@@ -2833,19 +2911,19 @@
       <c r="K8" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="62" t="str">
+      <c r="L8" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M8" s="62" t="str">
+      <c r="M8" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N8" s="62" t="str">
+      <c r="N8" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Vistorias</v>
       </c>
-      <c r="O8" s="62" t="str">
+      <c r="O8" s="58" t="str">
         <f t="shared" si="1"/>
         <v>De.Campo</v>
       </c>
@@ -2858,7 +2936,7 @@
       <c r="R8" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="S8" s="24" t="s">
+      <c r="S8" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T8" s="24" t="str">
@@ -2883,19 +2961,19 @@
       <c r="Y8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z8" s="67" t="s">
+      <c r="Z8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB8" s="67" t="s">
+      <c r="AB8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD8" s="67" t="s">
+      <c r="AD8" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2903,19 +2981,19 @@
       <c r="A9" s="35">
         <v>9</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="63" t="s">
+      <c r="E9" s="70" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="F9" s="70" t="s">
         <v>175</v>
       </c>
       <c r="G9" s="32" t="s">
@@ -2933,19 +3011,19 @@
       <c r="K9" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L9" s="62" t="str">
+      <c r="L9" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M9" s="62" t="str">
+      <c r="M9" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N9" s="62" t="str">
+      <c r="N9" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Imagens</v>
       </c>
-      <c r="O9" s="62" t="str">
+      <c r="O9" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Imagem.Banco</v>
       </c>
@@ -2958,7 +3036,7 @@
       <c r="R9" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="S9" s="24" t="s">
+      <c r="S9" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T9" s="24" t="str">
@@ -2983,19 +3061,19 @@
       <c r="Y9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z9" s="67" t="s">
+      <c r="Z9" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB9" s="67" t="s">
+      <c r="AB9" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="AD9" s="67" t="s">
+      <c r="AD9" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3003,19 +3081,19 @@
       <c r="A10" s="35">
         <v>10</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D10" s="63" t="s">
+      <c r="D10" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="63" t="s">
+      <c r="E10" s="70" t="s">
         <v>176</v>
       </c>
-      <c r="F10" s="63" t="s">
+      <c r="F10" s="70" t="s">
         <v>154</v>
       </c>
       <c r="G10" s="32" t="s">
@@ -3033,19 +3111,19 @@
       <c r="K10" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="62" t="str">
+      <c r="L10" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M10" s="62" t="str">
+      <c r="M10" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N10" s="62" t="str">
+      <c r="N10" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Imagens</v>
       </c>
-      <c r="O10" s="62" t="str">
+      <c r="O10" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Imagem.WayPoint</v>
       </c>
@@ -3058,7 +3136,7 @@
       <c r="R10" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="S10" s="24" t="s">
+      <c r="S10" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T10" s="24" t="str">
@@ -3083,19 +3161,19 @@
       <c r="Y10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z10" s="67" t="s">
+      <c r="Z10" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB10" s="67" t="s">
+      <c r="AB10" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="AD10" s="67" t="s">
+      <c r="AD10" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3103,19 +3181,19 @@
       <c r="A11" s="35">
         <v>11</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="70" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="63" t="s">
+      <c r="D11" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="70" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="63" t="s">
+      <c r="F11" s="70" t="s">
         <v>182</v>
       </c>
       <c r="G11" s="32" t="s">
@@ -3133,19 +3211,19 @@
       <c r="K11" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L11" s="62" t="str">
+      <c r="L11" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Operação</v>
       </c>
-      <c r="M11" s="62" t="str">
+      <c r="M11" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Manutenção</v>
       </c>
-      <c r="N11" s="62" t="str">
+      <c r="N11" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Imagens</v>
       </c>
-      <c r="O11" s="62" t="str">
+      <c r="O11" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Vídeo.Voo</v>
       </c>
@@ -3158,7 +3236,7 @@
       <c r="R11" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="S11" s="24" t="s">
+      <c r="S11" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T11" s="24" t="str">
@@ -3183,19 +3261,19 @@
       <c r="Y11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z11" s="67" t="s">
+      <c r="Z11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB11" s="67" t="s">
+      <c r="AB11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="AD11" s="67" t="s">
+      <c r="AD11" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3203,19 +3281,19 @@
       <c r="A12" s="35">
         <v>12</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="64" t="s">
+      <c r="D12" s="71" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="71" t="s">
         <v>198</v>
       </c>
-      <c r="F12" s="63" t="s">
+      <c r="F12" s="70" t="s">
         <v>185</v>
       </c>
       <c r="G12" s="32" t="s">
@@ -3233,19 +3311,19 @@
       <c r="K12" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="62" t="str">
+      <c r="L12" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Manutenção</v>
       </c>
-      <c r="M12" s="62" t="str">
+      <c r="M12" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Diagnósticas</v>
       </c>
-      <c r="N12" s="62" t="str">
+      <c r="N12" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Preventivas</v>
       </c>
-      <c r="O12" s="62" t="str">
+      <c r="O12" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Voo.Preventivo</v>
       </c>
@@ -3258,7 +3336,7 @@
       <c r="R12" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="S12" s="24" t="s">
+      <c r="S12" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T12" s="24" t="str">
@@ -3283,19 +3361,19 @@
       <c r="Y12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z12" s="67" t="s">
+      <c r="Z12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB12" s="67" t="s">
+      <c r="AB12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD12" s="67" t="s">
+      <c r="AD12" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3303,19 +3381,19 @@
       <c r="A13" s="35">
         <v>13</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="64" t="s">
+      <c r="C13" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="64" t="s">
+      <c r="D13" s="71" t="s">
         <v>201</v>
       </c>
-      <c r="E13" s="64" t="s">
+      <c r="E13" s="71" t="s">
         <v>199</v>
       </c>
-      <c r="F13" s="63" t="s">
+      <c r="F13" s="70" t="s">
         <v>184</v>
       </c>
       <c r="G13" s="32" t="s">
@@ -3333,19 +3411,19 @@
       <c r="K13" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="62" t="str">
+      <c r="L13" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Manutenção</v>
       </c>
-      <c r="M13" s="62" t="str">
+      <c r="M13" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Diagnósticas</v>
       </c>
-      <c r="N13" s="62" t="str">
+      <c r="N13" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Corretivas</v>
       </c>
-      <c r="O13" s="62" t="str">
+      <c r="O13" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Voo.Corretivo</v>
       </c>
@@ -3358,7 +3436,7 @@
       <c r="R13" s="24" t="s">
         <v>213</v>
       </c>
-      <c r="S13" s="24" t="s">
+      <c r="S13" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T13" s="24" t="str">
@@ -3383,19 +3461,19 @@
       <c r="Y13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z13" s="67" t="s">
+      <c r="Z13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB13" s="67" t="s">
+      <c r="AB13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD13" s="67" t="s">
+      <c r="AD13" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3403,19 +3481,19 @@
       <c r="A14" s="35">
         <v>14</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="C14" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="64" t="s">
+      <c r="D14" s="71" t="s">
         <v>201</v>
       </c>
-      <c r="E14" s="64" t="s">
+      <c r="E14" s="71" t="s">
         <v>200</v>
       </c>
-      <c r="F14" s="63" t="s">
+      <c r="F14" s="70" t="s">
         <v>183</v>
       </c>
       <c r="G14" s="32" t="s">
@@ -3433,19 +3511,19 @@
       <c r="K14" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L14" s="62" t="str">
+      <c r="L14" s="58" t="str">
         <f t="shared" si="0"/>
         <v>De.Manutenção</v>
       </c>
-      <c r="M14" s="62" t="str">
+      <c r="M14" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Diagnósticas</v>
       </c>
-      <c r="N14" s="62" t="str">
+      <c r="N14" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Preditivas</v>
       </c>
-      <c r="O14" s="62" t="str">
+      <c r="O14" s="58" t="str">
         <f t="shared" si="1"/>
         <v>Voo.Preditivo</v>
       </c>
@@ -3458,7 +3536,7 @@
       <c r="R14" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="S14" s="24" t="s">
+      <c r="S14" s="62" t="s">
         <v>9</v>
       </c>
       <c r="T14" s="24" t="str">
@@ -3483,95 +3561,88 @@
       <c r="Y14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="Z14" s="67" t="s">
+      <c r="Z14" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AB14" s="67" t="s">
+      <c r="AB14" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="AD14" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD14" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="35">
         <v>15</v>
       </c>
-      <c r="B15" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="63" t="s">
+      <c r="B15" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="D15" s="70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>254</v>
+      </c>
+      <c r="F15" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="D15" s="63" t="s">
+      <c r="G15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="M15" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="N15" s="59" t="s">
+        <v>255</v>
+      </c>
+      <c r="O15" s="59" t="s">
+        <v>256</v>
+      </c>
+      <c r="P15" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q15" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="E15" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="F15" s="63" t="s">
+      <c r="R15" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="G15" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="65" t="str">
-        <f t="shared" ref="L15:O19" si="4">SUBSTITUTE(CONCATENATE("", C15), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M15" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Macros</v>
-      </c>
-      <c r="N15" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O15" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P15" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q15" s="24" t="s">
-        <v>235</v>
-      </c>
-      <c r="R15" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="S15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T15" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>De API</v>
-      </c>
-      <c r="U15" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>Macros</v>
-      </c>
-      <c r="V15" s="66" t="str">
-        <f t="shared" si="2"/>
-        <v>Métodos</v>
+      <c r="S15" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="T15" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="U15" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="V15" s="60" t="s">
+        <v>255</v>
       </c>
       <c r="W15" s="34" t="s">
         <v>89</v>
@@ -3580,98 +3651,91 @@
         <f t="shared" si="3"/>
         <v>Key-UAS-15</v>
       </c>
-      <c r="Y15" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z15" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA15" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB15" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC15" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD15" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC15" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD15" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="35">
         <v>16</v>
       </c>
-      <c r="B16" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="63" t="s">
-        <v>230</v>
-      </c>
-      <c r="D16" s="63" t="s">
-        <v>232</v>
-      </c>
-      <c r="E16" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="F16" s="63" t="s">
+      <c r="B16" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="D16" s="70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="70" t="s">
+        <v>254</v>
+      </c>
+      <c r="F16" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="M16" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="N16" s="59" t="s">
+        <v>255</v>
+      </c>
+      <c r="O16" s="59" t="s">
+        <v>259</v>
+      </c>
+      <c r="P16" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q16" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="R16" s="24" t="s">
         <v>237</v>
       </c>
-      <c r="G16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>De API</v>
-      </c>
-      <c r="M16" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Macros</v>
-      </c>
-      <c r="N16" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O16" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P16" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q16" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="R16" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="S16" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T16" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>De API</v>
-      </c>
-      <c r="U16" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>Macros</v>
-      </c>
-      <c r="V16" s="66" t="str">
-        <f t="shared" si="2"/>
-        <v>Métodos</v>
+      <c r="S16" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="T16" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="U16" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="V16" s="60" t="s">
+        <v>255</v>
       </c>
       <c r="W16" s="34" t="s">
         <v>89</v>
@@ -3680,98 +3744,91 @@
         <f t="shared" si="3"/>
         <v>Key-UAS-16</v>
       </c>
-      <c r="Y16" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z16" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA16" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB16" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC16" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD16" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC16" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD16" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="35">
         <v>17</v>
       </c>
-      <c r="B17" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="63" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="63" t="s">
-        <v>232</v>
-      </c>
-      <c r="E17" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="F17" s="63" t="s">
+      <c r="B17" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>238</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="M17" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="N17" s="59" t="s">
+        <v>255</v>
+      </c>
+      <c r="O17" s="59" t="s">
+        <v>260</v>
+      </c>
+      <c r="P17" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="R17" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="G17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>De API</v>
-      </c>
-      <c r="M17" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Macros</v>
-      </c>
-      <c r="N17" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O17" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P17" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q17" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="R17" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="S17" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T17" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>De API</v>
-      </c>
-      <c r="U17" s="24" t="str">
-        <f t="shared" si="2"/>
-        <v>Macros</v>
-      </c>
-      <c r="V17" s="66" t="str">
-        <f t="shared" si="2"/>
-        <v>Métodos</v>
+      <c r="S17" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="T17" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="U17" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="V17" s="60" t="s">
+        <v>255</v>
       </c>
       <c r="W17" s="34" t="s">
         <v>89</v>
@@ -3780,98 +3837,91 @@
         <f t="shared" si="3"/>
         <v>Key-UAS-17</v>
       </c>
-      <c r="Y17" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z17" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA17" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB17" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC17" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD17" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD17" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="35">
         <v>18</v>
       </c>
-      <c r="B18" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="63" t="s">
-        <v>230</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>232</v>
-      </c>
-      <c r="E18" s="63" t="s">
-        <v>231</v>
-      </c>
-      <c r="F18" s="63" t="s">
+      <c r="B18" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="D18" s="70" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" s="70" t="s">
+        <v>254</v>
+      </c>
+      <c r="F18" s="70" t="s">
+        <v>242</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="M18" s="59" t="s">
+        <v>253</v>
+      </c>
+      <c r="N18" s="59" t="s">
+        <v>255</v>
+      </c>
+      <c r="O18" s="59" t="s">
+        <v>261</v>
+      </c>
+      <c r="P18" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="R18" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="G18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L18" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>De API</v>
-      </c>
-      <c r="M18" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Macros</v>
-      </c>
-      <c r="N18" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O18" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P18" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q18" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="R18" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="S18" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T18" s="24" t="str">
-        <f t="shared" ref="T18:V19" si="5">SUBSTITUTE(C18, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U18" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Macros</v>
-      </c>
-      <c r="V18" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Métodos</v>
+      <c r="S18" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="U18" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="V18" s="60" t="s">
+        <v>255</v>
       </c>
       <c r="W18" s="34" t="s">
         <v>89</v>
@@ -3880,98 +3930,91 @@
         <f t="shared" si="3"/>
         <v>Key-UAS-18</v>
       </c>
-      <c r="Y18" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z18" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA18" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB18" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC18" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD18" s="67" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC18" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD18" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="35">
         <v>19</v>
       </c>
-      <c r="B19" s="57" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="63" t="s">
-        <v>230</v>
-      </c>
-      <c r="D19" s="63" t="s">
-        <v>232</v>
-      </c>
-      <c r="E19" s="63" t="s">
+      <c r="B19" s="66" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="70" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="70" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="70" t="s">
+        <v>263</v>
+      </c>
+      <c r="F19" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="59" t="s">
+        <v>252</v>
+      </c>
+      <c r="M19" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="N19" s="59" t="s">
+        <v>264</v>
+      </c>
+      <c r="O19" s="59" t="s">
+        <v>265</v>
+      </c>
+      <c r="P19" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q19" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="R19" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="F19" s="63" t="s">
-        <v>250</v>
-      </c>
-      <c r="G19" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L19" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>De API</v>
-      </c>
-      <c r="M19" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Macros</v>
-      </c>
-      <c r="N19" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O19" s="65" t="str">
-        <f t="shared" si="4"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P19" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="Q19" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="R19" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="S19" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="T19" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>De API</v>
-      </c>
-      <c r="U19" s="24" t="str">
-        <f t="shared" si="5"/>
-        <v>Macros</v>
-      </c>
-      <c r="V19" s="66" t="str">
-        <f t="shared" si="5"/>
-        <v>Códigos Visuais</v>
+      <c r="S19" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="T19" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="U19" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="V19" s="60" t="s">
+        <v>264</v>
       </c>
       <c r="W19" s="34" t="s">
         <v>89</v>
@@ -3980,66 +4023,64 @@
         <f t="shared" si="3"/>
         <v>Key-UAS-19</v>
       </c>
-      <c r="Y19" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z19" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA19" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB19" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC19" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD19" s="67" t="s">
+      <c r="Y19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC19" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD19" s="61" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B19">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B13 B14 A14:A19">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19:F19">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="13" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F7 F1">
-    <cfRule type="duplicateValues" dxfId="6" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F14 F1 F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12:F14 F1 F3:F7 F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F18">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="2" priority="45" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="48" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F19">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -6684,7 +6725,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="181"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/ARQ/Ontologia_Drones.xlsx
+++ b/Versão5/ARQ/Ontologia_Drones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992AFFD0-1846-4C2C-A889-50F8F0133D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7821E170-7849-4378-89B2-323E97FD290C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,13 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="267">
-  <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="315">
   <si>
     <t>Valor</t>
   </si>
@@ -99,25 +93,7 @@
     <t>Escola Politécnica da UFRJ</t>
   </si>
   <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
-  </si>
-  <si>
     <t>DataHora</t>
-  </si>
-  <si>
-    <t>Advertência1</t>
   </si>
   <si>
     <t>Prédio</t>
@@ -872,13 +848,181 @@
   </si>
   <si>
     <t>API Macros Visuais</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Advertência</t>
+  </si>
+  <si>
+    <t>Aviso</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,8 +1105,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1101,6 +1253,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1150,10 +1314,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1364,47 +1529,39 @@
     <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1550,6 +1707,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1868,285 +2033,569 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="13" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.42578125" style="13" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="28" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
+      <c r="A1" s="72" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C1" s="26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="C4" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
+        <v>2</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46273.517005208334</v>
+        <v>46276.427755324075</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>26</v>
+        <v>264</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C20" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>265</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="6" t="str">
-        <f>_xlfn.TRANSLATE(B22,"pt","es")</f>
-        <v>Formalizar los datos de los vuelos de drones.</v>
+        <v>9</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="25" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B24" s="6" t="str">
-        <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="str">
+        <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
+        <v>Formalizar los datos para los vuelos de drones.</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="6" t="str">
+        <f>_xlfn.TRANSLATE(B24,"pt","en")</f>
         <v>Formalize data for drone flights.</v>
       </c>
-      <c r="C24" s="27" t="s">
-        <v>98</v>
+      <c r="C26" s="27" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B27" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B28" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B29" s="74" t="s">
+        <v>292</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B30" s="75" t="s">
+        <v>293</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B31" s="76" t="s">
+        <v>294</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B32" s="76" t="s">
+        <v>295</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B33" s="76" t="s">
+        <v>296</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B34" s="77" t="s">
+        <v>297</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B35" s="77" t="s">
+        <v>298</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B36" s="76" t="s">
+        <v>299</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B37" s="77" t="s">
+        <v>300</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B38" s="76" t="s">
+        <v>301</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B39" s="78" t="s">
+        <v>302</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B40" s="78" t="s">
+        <v>303</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B41" s="79" t="s">
+        <v>304</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A42" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B42" s="80" t="s">
+        <v>305</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A43" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B43" s="80" t="s">
+        <v>306</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B44" s="80" t="s">
+        <v>307</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B45" s="80" t="s">
+        <v>308</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B46" s="80" t="s">
+        <v>309</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B47" s="80" t="s">
+        <v>310</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A48" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B48" s="80" t="s">
+        <v>311</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A49" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B49" s="80" t="s">
+        <v>312</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{F67BA4A1-779A-445D-BD8E-85240B3BB385}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{A7BBA9B8-E794-42F4-809C-FDD2EE4E20C4}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{8073CFF2-5D6E-4193-9758-CA2B6F74B786}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{A85DC057-5C72-4BD3-845A-8E7E81A8BBF4}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{FF773A5B-6831-4B2E-9506-885B969BA853}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{8756EA82-8B46-404D-9A72-67DB35D174E2}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{7604CEAA-587C-4EB7-9D0B-25EF514A6497}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2187,94 +2636,94 @@
   <sheetData>
     <row r="1" spans="1:30" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B1" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="K1" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="L1" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="M1" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="33" t="s">
+      <c r="N1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="O1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="P1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="Q1" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="R1" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="T1" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="U1" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="O1" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="R1" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="S1" s="64" t="s">
-        <v>71</v>
-      </c>
-      <c r="T1" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="U1" s="19" t="s">
-        <v>72</v>
-      </c>
       <c r="V1" s="19" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="W1" s="19" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="X1" s="29" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="Y1" s="19" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="Z1" s="19" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AA1" s="19" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AB1" s="19" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="AC1" s="19" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="AD1" s="19" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" spans="1:30" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -2282,34 +2731,34 @@
         <v>2</v>
       </c>
       <c r="B2" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C2" s="67" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D2" s="67" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F2" s="69" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G2" s="57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" s="57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" s="57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J2" s="57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K2" s="57" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L2" s="58" t="str">
         <f t="shared" ref="L2:L14" si="0">_xlfn.CONCAT(C2)</f>
@@ -2328,19 +2777,19 @@
         <v>Data</v>
       </c>
       <c r="P2" s="58" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="Q2" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="R2" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="R2" s="24" t="s">
-        <v>202</v>
-      </c>
       <c r="S2" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" s="24" t="str">
-        <f t="shared" ref="T2:V17" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <f t="shared" ref="T2:V14" si="2">SUBSTITUTE(C2, ".", " ")</f>
         <v>De Tempo</v>
       </c>
       <c r="U2" s="24" t="str">
@@ -2352,29 +2801,29 @@
         <v>Calendários</v>
       </c>
       <c r="W2" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X2" s="30" t="str">
         <f>CONCATENATE("Key-UAS-",A2)</f>
         <v>Key-UAS-2</v>
       </c>
       <c r="Y2" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z2" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA2" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB2" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD2" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2382,34 +2831,34 @@
         <v>3</v>
       </c>
       <c r="B3" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C3" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D3" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F3" s="70" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G3" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L3" s="58" t="str">
         <f t="shared" si="0"/>
@@ -2428,16 +2877,16 @@
         <v>Drone</v>
       </c>
       <c r="P3" s="34" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="Q3" s="24" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="R3" s="24" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="S3" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T3" s="24" t="str">
         <f t="shared" si="2"/>
@@ -2452,29 +2901,29 @@
         <v>Vistorias</v>
       </c>
       <c r="W3" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X3" s="30" t="str">
         <f t="shared" ref="X3:X19" si="3">CONCATENATE("Key-UAS-",A3)</f>
         <v>Key-UAS-3</v>
       </c>
       <c r="Y3" s="24" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="Z3" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA3" s="24" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AB3" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC3" s="24" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AD3" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2482,34 +2931,34 @@
         <v>4</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C4" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D4" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E4" s="70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F4" s="70" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L4" s="58" t="str">
         <f t="shared" si="0"/>
@@ -2528,16 +2977,16 @@
         <v>Drone.LIDAR</v>
       </c>
       <c r="P4" s="34" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="S4" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" s="24" t="str">
         <f t="shared" si="2"/>
@@ -2552,29 +3001,29 @@
         <v>Vistorias</v>
       </c>
       <c r="W4" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X4" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-4</v>
       </c>
       <c r="Y4" s="24" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="Z4" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA4" s="24" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="AB4" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC4" s="24" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="AD4" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2582,34 +3031,34 @@
         <v>5</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C5" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D5" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E5" s="70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F5" s="70" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G5" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I5" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K5" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L5" s="58" t="str">
         <f t="shared" si="0"/>
@@ -2628,16 +3077,16 @@
         <v>Voo.Plano</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="S5" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T5" s="24" t="str">
         <f t="shared" si="2"/>
@@ -2652,29 +3101,29 @@
         <v>Vistorias</v>
       </c>
       <c r="W5" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X5" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-5</v>
       </c>
       <c r="Y5" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z5" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA5" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB5" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC5" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD5" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2682,34 +3131,34 @@
         <v>6</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D6" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F6" s="70" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G6" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I6" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L6" s="58" t="str">
         <f t="shared" si="0"/>
@@ -2728,16 +3177,16 @@
         <v>Voo.Autônomo</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="S6" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T6" s="24" t="str">
         <f t="shared" si="2"/>
@@ -2752,29 +3201,29 @@
         <v>Vistorias</v>
       </c>
       <c r="W6" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X6" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-6</v>
       </c>
       <c r="Y6" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z6" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA6" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB6" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC6" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD6" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2782,34 +3231,34 @@
         <v>7</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D7" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F7" s="70" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G7" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I7" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K7" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L7" s="58" t="str">
         <f t="shared" si="0"/>
@@ -2828,16 +3277,16 @@
         <v>Voo.Manual</v>
       </c>
       <c r="P7" s="34" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="R7" s="24" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="S7" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" s="24" t="str">
         <f t="shared" si="2"/>
@@ -2852,29 +3301,29 @@
         <v>Vistorias</v>
       </c>
       <c r="W7" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X7" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-7</v>
       </c>
       <c r="Y7" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA7" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB7" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC7" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD7" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2882,34 +3331,34 @@
         <v>8</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D8" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F8" s="70" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G8" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I8" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K8" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L8" s="58" t="str">
         <f t="shared" si="0"/>
@@ -2928,16 +3377,16 @@
         <v>De.Campo</v>
       </c>
       <c r="P8" s="34" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="S8" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" s="24" t="str">
         <f t="shared" si="2"/>
@@ -2952,29 +3401,29 @@
         <v>Vistorias</v>
       </c>
       <c r="W8" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X8" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-8</v>
       </c>
       <c r="Y8" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB8" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC8" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD8" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2982,34 +3431,34 @@
         <v>9</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D9" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F9" s="70" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G9" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K9" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L9" s="58" t="str">
         <f t="shared" si="0"/>
@@ -3028,16 +3477,16 @@
         <v>Imagem.Banco</v>
       </c>
       <c r="P9" s="34" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="Q9" s="24" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="S9" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" s="24" t="str">
         <f t="shared" si="2"/>
@@ -3052,29 +3501,29 @@
         <v>Imagens</v>
       </c>
       <c r="W9" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X9" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-9</v>
       </c>
       <c r="Y9" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z9" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA9" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB9" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC9" s="24" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="AD9" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3082,34 +3531,34 @@
         <v>10</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C10" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D10" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F10" s="70" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="G10" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H10" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I10" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K10" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L10" s="58" t="str">
         <f t="shared" si="0"/>
@@ -3128,16 +3577,16 @@
         <v>Imagem.WayPoint</v>
       </c>
       <c r="P10" s="34" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="R10" s="24" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="S10" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" s="24" t="str">
         <f t="shared" si="2"/>
@@ -3152,29 +3601,29 @@
         <v>Imagens</v>
       </c>
       <c r="W10" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X10" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-10</v>
       </c>
       <c r="Y10" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB10" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC10" s="24" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="AD10" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3182,34 +3631,34 @@
         <v>11</v>
       </c>
       <c r="B11" s="66" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C11" s="70" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="D11" s="70" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E11" s="70" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="F11" s="70" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="G11" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H11" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I11" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J11" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K11" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L11" s="58" t="str">
         <f t="shared" si="0"/>
@@ -3228,16 +3677,16 @@
         <v>Vídeo.Voo</v>
       </c>
       <c r="P11" s="34" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="R11" s="24" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="S11" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" s="24" t="str">
         <f t="shared" si="2"/>
@@ -3252,29 +3701,29 @@
         <v>Imagens</v>
       </c>
       <c r="W11" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X11" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-11</v>
       </c>
       <c r="Y11" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z11" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB11" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC11" s="24" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="AD11" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3282,34 +3731,34 @@
         <v>12</v>
       </c>
       <c r="B12" s="66" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C12" s="71" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D12" s="71" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E12" s="71" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F12" s="70" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G12" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H12" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I12" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J12" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K12" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L12" s="58" t="str">
         <f t="shared" si="0"/>
@@ -3328,16 +3777,16 @@
         <v>Voo.Preventivo</v>
       </c>
       <c r="P12" s="34" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="R12" s="24" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="S12" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" s="24" t="str">
         <f t="shared" si="2"/>
@@ -3352,29 +3801,29 @@
         <v>Preventivas</v>
       </c>
       <c r="W12" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X12" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-12</v>
       </c>
       <c r="Y12" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z12" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB12" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC12" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD12" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3382,34 +3831,34 @@
         <v>13</v>
       </c>
       <c r="B13" s="66" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C13" s="71" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E13" s="71" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F13" s="70" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G13" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H13" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I13" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J13" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K13" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L13" s="58" t="str">
         <f t="shared" si="0"/>
@@ -3428,16 +3877,16 @@
         <v>Voo.Corretivo</v>
       </c>
       <c r="P13" s="34" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="R13" s="24" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="S13" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" s="24" t="str">
         <f t="shared" si="2"/>
@@ -3452,29 +3901,29 @@
         <v>Corretivas</v>
       </c>
       <c r="W13" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X13" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-13</v>
       </c>
       <c r="Y13" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z13" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA13" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB13" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC13" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD13" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3482,34 +3931,34 @@
         <v>14</v>
       </c>
       <c r="B14" s="66" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C14" s="71" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D14" s="71" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E14" s="71" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F14" s="70" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="G14" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H14" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I14" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K14" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L14" s="58" t="str">
         <f t="shared" si="0"/>
@@ -3528,16 +3977,16 @@
         <v>Voo.Preditivo</v>
       </c>
       <c r="P14" s="34" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="S14" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" s="24" t="str">
         <f t="shared" si="2"/>
@@ -3552,29 +4001,29 @@
         <v>Preditivas</v>
       </c>
       <c r="W14" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X14" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-14</v>
       </c>
       <c r="Y14" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z14" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB14" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC14" s="24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD14" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3582,92 +4031,92 @@
         <v>15</v>
       </c>
       <c r="B15" s="66" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C15" s="70" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D15" s="70" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E15" s="70" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F15" s="70" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G15" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H15" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I15" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J15" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K15" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L15" s="59" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="M15" s="59" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="N15" s="59" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="O15" s="59" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="P15" s="24" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="S15" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" s="24" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="U15" s="24" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="V15" s="60" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W15" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X15" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-15</v>
       </c>
       <c r="Y15" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z15" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA15" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB15" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC15" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD15" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3675,92 +4124,92 @@
         <v>16</v>
       </c>
       <c r="B16" s="66" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="E16" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="F16" s="70" t="s">
+        <v>226</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="J16" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="59" t="s">
+        <v>244</v>
+      </c>
+      <c r="M16" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="N16" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="O16" s="59" t="s">
         <v>251</v>
       </c>
-      <c r="C16" s="70" t="s">
-        <v>252</v>
-      </c>
-      <c r="D16" s="70" t="s">
-        <v>253</v>
-      </c>
-      <c r="E16" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="F16" s="70" t="s">
-        <v>234</v>
-      </c>
-      <c r="G16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="M16" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="N16" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="O16" s="59" t="s">
-        <v>259</v>
-      </c>
       <c r="P16" s="24" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="S16" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" s="24" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="U16" s="24" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="V16" s="60" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W16" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X16" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-16</v>
       </c>
       <c r="Y16" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z16" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB16" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC16" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD16" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3768,92 +4217,92 @@
         <v>17</v>
       </c>
       <c r="B17" s="66" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C17" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="F17" s="70" t="s">
+        <v>230</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="J17" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="L17" s="59" t="s">
+        <v>244</v>
+      </c>
+      <c r="M17" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="N17" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="O17" s="59" t="s">
         <v>252</v>
       </c>
-      <c r="D17" s="70" t="s">
-        <v>253</v>
-      </c>
-      <c r="E17" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="F17" s="70" t="s">
-        <v>238</v>
-      </c>
-      <c r="G17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="M17" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="N17" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="O17" s="59" t="s">
-        <v>260</v>
-      </c>
       <c r="P17" s="24" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="S17" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17" s="24" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="U17" s="24" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="V17" s="60" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W17" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X17" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-17</v>
       </c>
       <c r="Y17" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z17" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA17" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB17" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC17" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD17" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3861,92 +4310,92 @@
         <v>18</v>
       </c>
       <c r="B18" s="66" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C18" s="70" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D18" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" s="70" t="s">
+        <v>246</v>
+      </c>
+      <c r="F18" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="L18" s="59" t="s">
+        <v>244</v>
+      </c>
+      <c r="M18" s="59" t="s">
+        <v>245</v>
+      </c>
+      <c r="N18" s="59" t="s">
+        <v>247</v>
+      </c>
+      <c r="O18" s="59" t="s">
         <v>253</v>
       </c>
-      <c r="E18" s="70" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" s="70" t="s">
-        <v>242</v>
-      </c>
-      <c r="G18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="L18" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="M18" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="N18" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="O18" s="59" t="s">
-        <v>261</v>
-      </c>
       <c r="P18" s="24" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="S18" s="62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T18" s="24" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="U18" s="24" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="V18" s="60" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="W18" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X18" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-18</v>
       </c>
       <c r="Y18" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z18" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA18" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB18" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC18" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD18" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3954,133 +4403,133 @@
         <v>19</v>
       </c>
       <c r="B19" s="66" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C19" s="70" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D19" s="70" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E19" s="70" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="F19" s="70" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G19" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I19" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J19" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K19" s="32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L19" s="59" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="M19" s="59" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="N19" s="59" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="O19" s="59" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="P19" s="24" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="Q19" s="24" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="R19" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="S19" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="T19" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="S19" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="T19" s="24" t="s">
-        <v>257</v>
-      </c>
       <c r="U19" s="24" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="V19" s="60" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="W19" s="34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="X19" s="30" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-19</v>
       </c>
       <c r="Y19" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z19" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA19" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB19" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC19" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD19" s="61" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:B13 B14 A14:A19">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="17" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2">
-    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F7 F1">
-    <cfRule type="duplicateValues" dxfId="10" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F14 F1 F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12:F14 F1 F3:F7 F20:F1048576">
-    <cfRule type="duplicateValues" dxfId="8" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F19">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="6" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="48" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R14">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F19">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -4105,64 +4554,64 @@
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="K1" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="L1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="M1" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="N1" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="O1" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="R1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="S1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>45</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
@@ -4170,64 +4619,64 @@
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4253,13 +4702,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4267,13 +4716,13 @@
         <v>2</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4317,85 +4766,85 @@
   <sheetData>
     <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D1" s="38" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="38" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="G1" s="38" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1" s="38" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="K1" s="38" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L1" s="37" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="M1" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N1" s="37" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P1" s="38" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Q1" s="38" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R1" s="38" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="S1" s="38" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T1" s="37" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="U1" s="37" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V1" s="40" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="W1" s="41" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="X1" s="42" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="Y1" s="41" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="Z1" s="42" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AA1" s="41" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4403,82 +4852,82 @@
         <v>2</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I2" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J2" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K2" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L2" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M2" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N2" s="51" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="O2" s="52" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="P2" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q2" s="52" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="R2" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S2" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T2" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U2" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V2" s="53" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="W2" s="55" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="X2" s="48" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="Y2" s="52" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="Z2" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA2" s="52" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4486,82 +4935,82 @@
         <v>3</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E3" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G3" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I3" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J3" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K3" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L3" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="N3" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="O3" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q3" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="R3" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="T3" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="V3" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="W3" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="X3" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y3" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z3" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="M3" s="49" t="s">
-        <v>112</v>
-      </c>
-      <c r="N3" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q3" s="52" t="s">
-        <v>195</v>
-      </c>
-      <c r="R3" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="T3" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="U3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="W3" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="X3" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="48" t="s">
-        <v>119</v>
-      </c>
       <c r="AA3" s="52" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4569,82 +5018,82 @@
         <v>4</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E4" s="54" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G4" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I4" s="54" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J4" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L4" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M4" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N4" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O4" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P4" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q4" s="52" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="R4" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S4" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U4" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V4" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W4" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X4" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y4" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z4" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA4" s="52" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4652,82 +5101,82 @@
         <v>5</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="F5" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I5" s="54" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J5" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K5" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L5" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M5" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N5" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O5" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P5" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q5" s="52" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="R5" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S5" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T5" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U5" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V5" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W5" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X5" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y5" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z5" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA5" s="52" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4735,82 +5184,82 @@
         <v>6</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E6" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G6" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H6" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I6" s="54" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J6" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L6" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="M6" s="49" t="s">
+        <v>114</v>
+      </c>
+      <c r="N6" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="P6" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q6" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="R6" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="S6" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="T6" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="U6" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="V6" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="W6" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="X6" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y6" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z6" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="M6" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="N6" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q6" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="R6" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="T6" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="U6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="V6" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="W6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="X6" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="48" t="s">
-        <v>119</v>
-      </c>
       <c r="AA6" s="52" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4818,82 +5267,82 @@
         <v>7</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E7" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F7" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G7" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I7" s="54" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="J7" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K7" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L7" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="M7" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="N7" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="O7" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="P7" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q7" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="R7" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="S7" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="T7" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="U7" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="V7" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="W7" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="X7" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y7" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z7" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="M7" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="N7" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P7" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q7" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="R7" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="T7" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="U7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="V7" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="W7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="X7" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="48" t="s">
-        <v>119</v>
-      </c>
       <c r="AA7" s="52" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4901,82 +5350,82 @@
         <v>8</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G8" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H8" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I8" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J8" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K8" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L8" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M8" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N8" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O8" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P8" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R8" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S8" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U8" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V8" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W8" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X8" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y8" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA8" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4984,82 +5433,82 @@
         <v>9</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E9" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H9" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I9" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J9" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K9" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L9" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M9" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N9" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O9" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R9" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S9" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T9" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U9" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V9" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W9" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X9" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y9" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z9" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA9" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5067,82 +5516,82 @@
         <v>10</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E10" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G10" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H10" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I10" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J10" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K10" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L10" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M10" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N10" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O10" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R10" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S10" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U10" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V10" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W10" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X10" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y10" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA10" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5150,82 +5599,82 @@
         <v>11</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G11" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H11" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I11" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J11" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K11" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L11" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M11" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N11" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O11" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R11" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S11" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T11" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U11" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V11" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W11" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X11" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y11" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z11" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA11" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5233,82 +5682,82 @@
         <v>12</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E12" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G12" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H12" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I12" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J12" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K12" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L12" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M12" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N12" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O12" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R12" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S12" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U12" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V12" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W12" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X12" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z12" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA12" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5316,82 +5765,82 @@
         <v>13</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E13" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G13" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H13" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I13" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J13" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K13" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L13" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M13" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N13" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O13" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R13" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S13" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U13" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V13" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W13" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X13" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y13" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z13" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA13" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5399,82 +5848,82 @@
         <v>14</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G14" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H14" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I14" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J14" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K14" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L14" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M14" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N14" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O14" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R14" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S14" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U14" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V14" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W14" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X14" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y14" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z14" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA14" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5482,82 +5931,82 @@
         <v>15</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G15" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H15" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I15" s="54" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J15" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K15" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L15" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M15" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N15" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O15" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="R15" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S15" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U15" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V15" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W15" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X15" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y15" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z15" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA15" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5565,82 +6014,82 @@
         <v>16</v>
       </c>
       <c r="B16" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I16" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="M16" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="N16" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="O16" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="P16" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q16" s="52" t="s">
         <v>165</v>
       </c>
-      <c r="C16" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="D16" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="I16" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="J16" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M16" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N16" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O16" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P16" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q16" s="52" t="s">
-        <v>173</v>
-      </c>
       <c r="R16" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S16" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T16" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U16" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V16" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W16" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X16" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y16" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z16" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA16" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5648,82 +6097,82 @@
         <v>17</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G17" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H17" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="I17" s="54" t="s">
-        <v>124</v>
-      </c>
       <c r="J17" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K17" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L17" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M17" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N17" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O17" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="R17" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S17" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T17" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U17" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V17" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W17" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y17" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z17" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA17" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5731,82 +6180,82 @@
         <v>18</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E18" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G18" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H18" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I18" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="I18" s="54" t="s">
-        <v>124</v>
-      </c>
       <c r="J18" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K18" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L18" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M18" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N18" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O18" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q18" s="52" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="R18" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S18" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T18" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U18" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V18" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W18" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X18" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y18" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z18" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA18" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5814,82 +6263,82 @@
         <v>19</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G19" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H19" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="I19" s="54" t="s">
-        <v>124</v>
-      </c>
       <c r="J19" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K19" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L19" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M19" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N19" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O19" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P19" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q19" s="52" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="R19" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S19" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T19" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U19" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V19" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W19" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X19" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y19" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z19" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA19" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5897,82 +6346,82 @@
         <v>20</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F20" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G20" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H20" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="I20" s="54" t="s">
-        <v>124</v>
-      </c>
       <c r="J20" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K20" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L20" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M20" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N20" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O20" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q20" s="52" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="R20" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S20" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T20" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U20" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V20" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W20" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X20" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y20" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z20" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA20" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5980,82 +6429,82 @@
         <v>21</v>
       </c>
       <c r="B21" s="44" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G21" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H21" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="I21" s="54" t="s">
-        <v>124</v>
-      </c>
       <c r="J21" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K21" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L21" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M21" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N21" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O21" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P21" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q21" s="52" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="R21" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S21" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T21" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U21" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V21" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W21" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X21" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y21" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z21" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA21" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6063,82 +6512,82 @@
         <v>22</v>
       </c>
       <c r="B22" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G22" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="H22" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="54" t="s">
+        <v>116</v>
+      </c>
+      <c r="J22" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="L22" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="M22" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="N22" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="O22" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="P22" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q22" s="52" t="s">
+        <v>165</v>
+      </c>
+      <c r="R22" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="S22" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="T22" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="U22" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="V22" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="W22" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="X22" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y22" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z22" s="48" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA22" s="52" t="s">
         <v>171</v>
-      </c>
-      <c r="C22" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="D22" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="I22" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="J22" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="K22" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="L22" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M22" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N22" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O22" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P22" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q22" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="R22" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="S22" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="T22" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="U22" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="V22" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="W22" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="X22" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y22" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z22" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA22" s="52" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6146,82 +6595,82 @@
         <v>23</v>
       </c>
       <c r="B23" s="44" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C23" s="45" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E23" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G23" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H23" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="I23" s="54" t="s">
-        <v>124</v>
-      </c>
       <c r="J23" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K23" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L23" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M23" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N23" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O23" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P23" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q23" s="52" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="R23" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S23" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T23" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U23" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V23" s="53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W23" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X23" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y23" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z23" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA23" s="52" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6229,82 +6678,82 @@
         <v>24</v>
       </c>
       <c r="B24" s="44" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C24" s="45" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E24" s="54" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F24" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G24" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H24" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I24" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J24" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K24" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L24" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M24" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N24" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O24" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P24" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q24" s="52" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="R24" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S24" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U24" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V24" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W24" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X24" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y24" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z24" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA24" s="52" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6312,82 +6761,82 @@
         <v>25</v>
       </c>
       <c r="B25" s="44" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C25" s="45" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E25" s="54" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F25" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G25" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H25" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I25" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K25" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L25" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M25" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N25" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O25" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P25" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="52" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="R25" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S25" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T25" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U25" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V25" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W25" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X25" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y25" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z25" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA25" s="52" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6395,82 +6844,82 @@
         <v>26</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C26" s="45" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F26" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G26" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H26" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I26" s="54" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K26" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L26" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M26" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N26" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O26" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P26" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q26" s="52" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="R26" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S26" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T26" s="48" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="U26" s="56" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="V26" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W26" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X26" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y26" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA26" s="52" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6478,82 +6927,82 @@
         <v>27</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C27" s="45" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E27" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F27" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G27" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H27" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I27" s="54" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="J27" s="46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K27" s="47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L27" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M27" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N27" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O27" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P27" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="52" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="R27" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S27" s="50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T27" s="48" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="U27" s="56" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="V27" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W27" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X27" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y27" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z27" s="48" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="AA27" s="52" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6561,82 +7010,82 @@
         <v>28</v>
       </c>
       <c r="B28" s="44" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C28" s="45" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E28" s="54" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G28" s="54" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H28" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I28" s="47" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J28" s="46" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="K28" s="47" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="L28" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M28" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N28" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O28" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P28" s="51" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="Q28" s="52" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="R28" s="51" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="S28" s="52" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="T28" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U28" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V28" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W28" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X28" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y28" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z28" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA28" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6644,88 +7093,88 @@
         <v>29</v>
       </c>
       <c r="B29" s="44" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C29" s="45" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E29" s="54" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F29" s="46" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G29" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="J29" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="K29" s="47" t="s">
+        <v>112</v>
+      </c>
+      <c r="L29" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="M29" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="N29" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="O29" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="P29" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q29" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="H29" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="I29" s="47" t="s">
-        <v>124</v>
-      </c>
-      <c r="J29" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="K29" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="L29" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="M29" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="N29" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="O29" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="P29" s="51" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q29" s="52" t="s">
-        <v>144</v>
-      </c>
       <c r="R29" s="51" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="S29" s="52" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="T29" s="51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U29" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V29" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W29" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X29" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y29" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z29" s="48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA29" s="52" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B29">
-    <cfRule type="duplicateValues" dxfId="4" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
